--- a/research/traditional_assets/database/data/portugal/portugal_steel.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_steel.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.104014186154114</v>
+        <v>0.1038313063631904</v>
       </c>
       <c r="C2">
-        <v>200.5425681859059</v>
+        <v>198.9237371028675</v>
       </c>
       <c r="D2">
-        <v>159.7425681859059</v>
+        <v>160.1447371028675</v>
       </c>
       <c r="E2">
-        <v>-18.4</v>
+        <v>-16.379</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.021</v>
       </c>
       <c r="G2">
         <v>40.8</v>
@@ -1451,28 +1451,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1016563</v>
       </c>
       <c r="N2">
-        <v>17.52061224489796</v>
+        <v>17.41895594489796</v>
       </c>
       <c r="O2">
-        <v>3.679328571428572</v>
+        <v>3.657980748428572</v>
       </c>
       <c r="P2">
-        <v>13.84128367346939</v>
+        <v>13.76097519646939</v>
       </c>
       <c r="Q2">
-        <v>17.85128367346939</v>
+        <v>17.77097519646939</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.104014186154114</v>
+        <v>0.1044787235991822</v>
       </c>
       <c r="T2">
-        <v>0.9815748103161357</v>
+        <v>0.9894075790045169</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>172.3514651319984</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1038313063631904</v>
+        <v>0.1036484265722668</v>
       </c>
       <c r="C3">
-        <v>198.9237371028675</v>
+        <v>197.3069361369683</v>
       </c>
       <c r="D3">
-        <v>160.1447371028675</v>
+        <v>160.5489361369683</v>
       </c>
       <c r="E3">
-        <v>-16.379</v>
+        <v>-14.358</v>
       </c>
       <c r="F3">
-        <v>2.021</v>
+        <v>4.042</v>
       </c>
       <c r="G3">
         <v>40.8</v>
@@ -1533,28 +1533,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M3">
-        <v>0.1016563</v>
+        <v>0.2033126</v>
       </c>
       <c r="N3">
-        <v>17.41895594489796</v>
+        <v>17.31729964489796</v>
       </c>
       <c r="O3">
-        <v>3.657980748428572</v>
+        <v>3.636632925428572</v>
       </c>
       <c r="P3">
-        <v>13.76097519646939</v>
+        <v>13.68066671946939</v>
       </c>
       <c r="Q3">
-        <v>17.77097519646939</v>
+        <v>17.69066671946939</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1044787235991822</v>
+        <v>0.1049527414002722</v>
       </c>
       <c r="T3">
-        <v>0.9894075790045169</v>
+        <v>0.9974002001151102</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>172.3514651319984</v>
+        <v>86.17573256599917</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1036484265722668</v>
+        <v>0.1034655467813431</v>
       </c>
       <c r="C4">
-        <v>197.3069361369683</v>
+        <v>195.6921806989126</v>
       </c>
       <c r="D4">
-        <v>160.5489361369683</v>
+        <v>160.9551806989126</v>
       </c>
       <c r="E4">
-        <v>-14.358</v>
+        <v>-12.337</v>
       </c>
       <c r="F4">
-        <v>4.042</v>
+        <v>6.063</v>
       </c>
       <c r="G4">
         <v>40.8</v>
@@ -1615,28 +1615,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M4">
-        <v>0.2033126</v>
+        <v>0.3049689</v>
       </c>
       <c r="N4">
-        <v>17.31729964489796</v>
+        <v>17.21564334489796</v>
       </c>
       <c r="O4">
-        <v>3.636632925428572</v>
+        <v>3.615285102428572</v>
       </c>
       <c r="P4">
-        <v>13.68066671946939</v>
+        <v>13.60035824246939</v>
       </c>
       <c r="Q4">
-        <v>17.69066671946939</v>
+        <v>17.61035824246939</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1049527414002722</v>
+        <v>0.1054365327642713</v>
       </c>
       <c r="T4">
-        <v>0.9974002001151102</v>
+        <v>1.005557617537262</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>86.17573256599917</v>
+        <v>57.45048837733278</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1034655467813431</v>
+        <v>0.1032826669904195</v>
       </c>
       <c r="C5">
-        <v>195.6921806989126</v>
+        <v>194.0794863557777</v>
       </c>
       <c r="D5">
-        <v>160.9551806989126</v>
+        <v>161.3634863557777</v>
       </c>
       <c r="E5">
-        <v>-12.337</v>
+        <v>-10.316</v>
       </c>
       <c r="F5">
-        <v>6.063</v>
+        <v>8.084</v>
       </c>
       <c r="G5">
         <v>40.8</v>
@@ -1697,28 +1697,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M5">
-        <v>0.3049689</v>
+        <v>0.4066252</v>
       </c>
       <c r="N5">
-        <v>17.21564334489796</v>
+        <v>17.11398704489796</v>
       </c>
       <c r="O5">
-        <v>3.615285102428572</v>
+        <v>3.593937279428572</v>
       </c>
       <c r="P5">
-        <v>13.60035824246939</v>
+        <v>13.52004976546939</v>
       </c>
       <c r="Q5">
-        <v>17.61035824246939</v>
+        <v>17.53004976546939</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1054365327642713</v>
+        <v>0.1059304031150203</v>
       </c>
       <c r="T5">
-        <v>1.005557617537262</v>
+        <v>1.013884981155708</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>57.45048837733278</v>
+        <v>43.08786628299958</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1032826669904195</v>
+        <v>0.1030997871994958</v>
       </c>
       <c r="C6">
-        <v>194.0794863557777</v>
+        <v>192.4688688330031</v>
       </c>
       <c r="D6">
-        <v>161.3634863557777</v>
+        <v>161.7738688330031</v>
       </c>
       <c r="E6">
-        <v>-10.316</v>
+        <v>-8.294999999999998</v>
       </c>
       <c r="F6">
-        <v>8.084</v>
+        <v>10.105</v>
       </c>
       <c r="G6">
         <v>40.8</v>
@@ -1779,28 +1779,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M6">
-        <v>0.4066252</v>
+        <v>0.5082814999999999</v>
       </c>
       <c r="N6">
-        <v>17.11398704489796</v>
+        <v>17.01233074489796</v>
       </c>
       <c r="O6">
-        <v>3.593937279428572</v>
+        <v>3.572589456428572</v>
       </c>
       <c r="P6">
-        <v>13.52004976546939</v>
+        <v>13.43974128846939</v>
       </c>
       <c r="Q6">
-        <v>17.53004976546939</v>
+        <v>17.44974128846939</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1059304031150203</v>
+        <v>0.1064346707363114</v>
       </c>
       <c r="T6">
-        <v>1.013884981155708</v>
+        <v>1.022387657692438</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>43.08786628299958</v>
+        <v>34.47029302639967</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1030997871994958</v>
+        <v>0.1029169074085722</v>
       </c>
       <c r="C7">
-        <v>192.4688688330031</v>
+        <v>190.8603440164087</v>
       </c>
       <c r="D7">
-        <v>161.7738688330031</v>
+        <v>162.1863440164087</v>
       </c>
       <c r="E7">
-        <v>-8.294999999999998</v>
+        <v>-6.273999999999997</v>
       </c>
       <c r="F7">
-        <v>10.105</v>
+        <v>12.126</v>
       </c>
       <c r="G7">
         <v>40.8</v>
@@ -1861,28 +1861,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M7">
-        <v>0.5082814999999999</v>
+        <v>0.6099378000000001</v>
       </c>
       <c r="N7">
-        <v>17.01233074489796</v>
+        <v>16.91067444489796</v>
       </c>
       <c r="O7">
-        <v>3.572589456428572</v>
+        <v>3.551241633428571</v>
       </c>
       <c r="P7">
-        <v>13.43974128846939</v>
+        <v>13.35943281146939</v>
       </c>
       <c r="Q7">
-        <v>17.44974128846939</v>
+        <v>17.36943281146939</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1064346707363114</v>
+        <v>0.1069496674559279</v>
       </c>
       <c r="T7">
-        <v>1.022387657692438</v>
+        <v>1.031071242240588</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>34.47029302639967</v>
+        <v>28.72524418866638</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1029169074085722</v>
+        <v>0.1027340276176486</v>
       </c>
       <c r="C8">
-        <v>190.8603440164087</v>
+        <v>189.2539279542453</v>
       </c>
       <c r="D8">
-        <v>162.1863440164087</v>
+        <v>162.6009279542453</v>
       </c>
       <c r="E8">
-        <v>-6.273999999999999</v>
+        <v>-4.253</v>
       </c>
       <c r="F8">
-        <v>12.126</v>
+        <v>14.147</v>
       </c>
       <c r="G8">
         <v>40.8</v>
@@ -1943,28 +1943,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M8">
-        <v>0.6099378</v>
+        <v>0.7115940999999999</v>
       </c>
       <c r="N8">
-        <v>16.91067444489796</v>
+        <v>16.80901814489796</v>
       </c>
       <c r="O8">
-        <v>3.551241633428571</v>
+        <v>3.529893810428572</v>
       </c>
       <c r="P8">
-        <v>13.35943281146939</v>
+        <v>13.27912433446939</v>
       </c>
       <c r="Q8">
-        <v>17.36943281146939</v>
+        <v>17.28912433446939</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1069496674559279</v>
+        <v>0.1074757393738157</v>
       </c>
       <c r="T8">
-        <v>1.031071242240588</v>
+        <v>1.039941570542461</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.72524418866639</v>
+        <v>24.62163787599977</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1027340276176486</v>
+        <v>0.1025511478267249</v>
       </c>
       <c r="C9">
-        <v>189.2539279542453</v>
+        <v>187.6496368592756</v>
       </c>
       <c r="D9">
-        <v>162.6009279542453</v>
+        <v>163.0176368592756</v>
       </c>
       <c r="E9">
-        <v>-4.252999999999998</v>
+        <v>-2.231999999999999</v>
       </c>
       <c r="F9">
-        <v>14.147</v>
+        <v>16.168</v>
       </c>
       <c r="G9">
         <v>40.8</v>
@@ -2025,28 +2025,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M9">
-        <v>0.7115941</v>
+        <v>0.8132503999999999</v>
       </c>
       <c r="N9">
-        <v>16.80901814489796</v>
+        <v>16.70736184489796</v>
       </c>
       <c r="O9">
-        <v>3.529893810428572</v>
+        <v>3.508545987428572</v>
       </c>
       <c r="P9">
-        <v>13.27912433446939</v>
+        <v>13.19881585746939</v>
       </c>
       <c r="Q9">
-        <v>17.28912433446939</v>
+        <v>17.20881585746939</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1074757393738157</v>
+        <v>0.1080132476377445</v>
       </c>
       <c r="T9">
-        <v>1.039941570542461</v>
+        <v>1.049004732068288</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.62163787599976</v>
+        <v>21.54393314149979</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1025511478267249</v>
+        <v>0.1023682680358013</v>
       </c>
       <c r="C10">
-        <v>187.6496368592756</v>
+        <v>186.0474871108876</v>
       </c>
       <c r="D10">
-        <v>163.0176368592756</v>
+        <v>163.4364871108876</v>
       </c>
       <c r="E10">
-        <v>-2.231999999999999</v>
+        <v>-0.2109999999999985</v>
       </c>
       <c r="F10">
-        <v>16.168</v>
+        <v>18.189</v>
       </c>
       <c r="G10">
         <v>40.8</v>
@@ -2107,28 +2107,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M10">
-        <v>0.8132503999999999</v>
+        <v>0.9149067</v>
       </c>
       <c r="N10">
-        <v>16.70736184489796</v>
+        <v>16.60570554489796</v>
       </c>
       <c r="O10">
-        <v>3.508545987428572</v>
+        <v>3.487198164428572</v>
       </c>
       <c r="P10">
-        <v>13.19881585746939</v>
+        <v>13.11850738046939</v>
       </c>
       <c r="Q10">
-        <v>17.20881585746939</v>
+        <v>17.12850738046939</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1080132476377445</v>
+        <v>0.1085625692701113</v>
       </c>
       <c r="T10">
-        <v>1.049004732068288</v>
+        <v>1.058267083957319</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.54393314149979</v>
+        <v>19.15016279244426</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1023682680358013</v>
+        <v>0.1021853882448776</v>
       </c>
       <c r="C11">
-        <v>186.0474871108876</v>
+        <v>184.4474952572408</v>
       </c>
       <c r="D11">
-        <v>163.4364871108876</v>
+        <v>163.8574952572408</v>
       </c>
       <c r="E11">
-        <v>-0.2109999999999985</v>
+        <v>1.809999999999999</v>
       </c>
       <c r="F11">
-        <v>18.189</v>
+        <v>20.21</v>
       </c>
       <c r="G11">
         <v>40.8</v>
@@ -2189,28 +2189,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M11">
-        <v>0.9149067</v>
+        <v>1.016563</v>
       </c>
       <c r="N11">
-        <v>16.60570554489796</v>
+        <v>16.50404924489796</v>
       </c>
       <c r="O11">
-        <v>3.487198164428572</v>
+        <v>3.465850341428571</v>
       </c>
       <c r="P11">
-        <v>13.11850738046939</v>
+        <v>13.03819890346939</v>
       </c>
       <c r="Q11">
-        <v>17.12850738046939</v>
+        <v>17.04819890346939</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1085625692701113</v>
+        <v>0.109124098049864</v>
       </c>
       <c r="T11">
-        <v>1.058267083957319</v>
+        <v>1.06773526588833</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.15016279244426</v>
+        <v>17.23514651319983</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1021853882448776</v>
+        <v>0.102002508453954</v>
       </c>
       <c r="C12">
-        <v>184.4474952572408</v>
+        <v>182.8496780174456</v>
       </c>
       <c r="D12">
-        <v>163.8574952572408</v>
+        <v>164.2806780174456</v>
       </c>
       <c r="E12">
-        <v>1.810000000000002</v>
+        <v>3.831</v>
       </c>
       <c r="F12">
-        <v>20.21</v>
+        <v>22.231</v>
       </c>
       <c r="G12">
         <v>40.8</v>
@@ -2271,28 +2271,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M12">
-        <v>1.016563</v>
+        <v>1.1182193</v>
       </c>
       <c r="N12">
-        <v>16.50404924489796</v>
+        <v>16.40239294489796</v>
       </c>
       <c r="O12">
-        <v>3.465850341428571</v>
+        <v>3.444502518428572</v>
       </c>
       <c r="P12">
-        <v>13.03819890346939</v>
+        <v>12.95789042646939</v>
       </c>
       <c r="Q12">
-        <v>17.04819890346939</v>
+        <v>16.96789042646939</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.109124098049864</v>
+        <v>0.1096982454538809</v>
       </c>
       <c r="T12">
-        <v>1.06773526588833</v>
+        <v>1.077416215952621</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.23514651319983</v>
+        <v>15.66831501199985</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.102002508453954</v>
+        <v>0.1018196286630304</v>
       </c>
       <c r="C13">
-        <v>182.8496780174456</v>
+        <v>181.2540522837767</v>
       </c>
       <c r="D13">
-        <v>164.2806780174456</v>
+        <v>164.7060522837767</v>
       </c>
       <c r="E13">
-        <v>3.831</v>
+        <v>5.852</v>
       </c>
       <c r="F13">
-        <v>22.231</v>
+        <v>24.252</v>
       </c>
       <c r="G13">
         <v>40.8</v>
@@ -2353,28 +2353,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M13">
-        <v>1.1182193</v>
+        <v>1.2198756</v>
       </c>
       <c r="N13">
-        <v>16.40239294489796</v>
+        <v>16.30073664489796</v>
       </c>
       <c r="O13">
-        <v>3.444502518428572</v>
+        <v>3.423154695428571</v>
       </c>
       <c r="P13">
-        <v>12.95789042646939</v>
+        <v>12.87758194946939</v>
       </c>
       <c r="Q13">
-        <v>16.96789042646939</v>
+        <v>16.88758194946939</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1096982454538809</v>
+        <v>0.1102854416625345</v>
       </c>
       <c r="T13">
-        <v>1.077416215952621</v>
+        <v>1.087317187609283</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.66831501199985</v>
+        <v>14.36262209433319</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1018196286630304</v>
+        <v>0.1016367488721067</v>
       </c>
       <c r="C14">
-        <v>181.2540522837767</v>
+        <v>179.6606351239203</v>
       </c>
       <c r="D14">
-        <v>164.7060522837767</v>
+        <v>165.1336351239203</v>
       </c>
       <c r="E14">
-        <v>5.852</v>
+        <v>7.873000000000001</v>
       </c>
       <c r="F14">
-        <v>24.252</v>
+        <v>26.273</v>
       </c>
       <c r="G14">
         <v>40.8</v>
@@ -2435,28 +2435,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M14">
-        <v>1.2198756</v>
+        <v>1.3215319</v>
       </c>
       <c r="N14">
-        <v>16.30073664489796</v>
+        <v>16.19908034489796</v>
       </c>
       <c r="O14">
-        <v>3.423154695428571</v>
+        <v>3.401806872428572</v>
       </c>
       <c r="P14">
-        <v>12.87758194946939</v>
+        <v>12.79727347246939</v>
       </c>
       <c r="Q14">
-        <v>16.88758194946939</v>
+        <v>16.80727347246939</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1102854416625345</v>
+        <v>0.1108861366346054</v>
       </c>
       <c r="T14">
-        <v>1.087317187609283</v>
+        <v>1.097445767809776</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.36262209433319</v>
+        <v>13.25780501015372</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1016367488721067</v>
+        <v>0.1016197690811831</v>
       </c>
       <c r="C15">
-        <v>179.6606351239203</v>
+        <v>177.6794474511312</v>
       </c>
       <c r="D15">
-        <v>165.1336351239203</v>
+        <v>165.1734474511312</v>
       </c>
       <c r="E15">
-        <v>7.873000000000001</v>
+        <v>9.894000000000002</v>
       </c>
       <c r="F15">
-        <v>26.273</v>
+        <v>28.294</v>
       </c>
       <c r="G15">
         <v>40.8</v>
@@ -2517,45 +2517,45 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M15">
-        <v>1.3215319</v>
+        <v>1.4656292</v>
       </c>
       <c r="N15">
-        <v>16.19908034489796</v>
+        <v>16.05498304489796</v>
       </c>
       <c r="O15">
-        <v>3.401806872428572</v>
+        <v>3.371546439428572</v>
       </c>
       <c r="P15">
-        <v>12.79727347246939</v>
+        <v>12.68343660546939</v>
       </c>
       <c r="Q15">
-        <v>16.80727347246939</v>
+        <v>16.69343660546939</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1108861366346054</v>
+        <v>0.1115008012571896</v>
       </c>
       <c r="T15">
-        <v>1.097445767809776</v>
+        <v>1.107809896387025</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.21</v>
       </c>
       <c r="W15">
-        <v>0.039737</v>
+        <v>0.040922</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.25780501015372</v>
+        <v>11.95432804211185</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1016197690811831</v>
+        <v>0.1014487392902594</v>
       </c>
       <c r="C16">
-        <v>177.6794474511312</v>
+        <v>176.060532208461</v>
       </c>
       <c r="D16">
-        <v>165.1734474511312</v>
+        <v>165.575532208461</v>
       </c>
       <c r="E16">
-        <v>9.894000000000002</v>
+        <v>11.91500000000001</v>
       </c>
       <c r="F16">
-        <v>28.294</v>
+        <v>30.315</v>
       </c>
       <c r="G16">
         <v>40.8</v>
@@ -2599,28 +2599,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M16">
-        <v>1.4656292</v>
+        <v>1.570317</v>
       </c>
       <c r="N16">
-        <v>16.05498304489796</v>
+        <v>15.95029524489796</v>
       </c>
       <c r="O16">
-        <v>3.371546439428572</v>
+        <v>3.349562001428572</v>
       </c>
       <c r="P16">
-        <v>12.68343660546939</v>
+        <v>12.60073324346939</v>
       </c>
       <c r="Q16">
-        <v>16.69343660546939</v>
+        <v>16.61073324346939</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1115008012571896</v>
+        <v>0.1121299285767758</v>
       </c>
       <c r="T16">
-        <v>1.107809896387025</v>
+        <v>1.11841788681315</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.95432804211185</v>
+        <v>11.1573728393044</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1014487392902594</v>
+        <v>0.1012777094993358</v>
       </c>
       <c r="C17">
-        <v>176.060532208461</v>
+        <v>174.4435793474744</v>
       </c>
       <c r="D17">
-        <v>165.575532208461</v>
+        <v>165.9795793474745</v>
       </c>
       <c r="E17">
-        <v>11.915</v>
+        <v>13.936</v>
       </c>
       <c r="F17">
-        <v>30.315</v>
+        <v>32.336</v>
       </c>
       <c r="G17">
         <v>40.8</v>
@@ -2681,28 +2681,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M17">
-        <v>1.570317</v>
+        <v>1.6750048</v>
       </c>
       <c r="N17">
-        <v>15.95029524489796</v>
+        <v>15.84560744489796</v>
       </c>
       <c r="O17">
-        <v>3.349562001428572</v>
+        <v>3.327577563428572</v>
       </c>
       <c r="P17">
-        <v>12.60073324346939</v>
+        <v>12.51802988146939</v>
       </c>
       <c r="Q17">
-        <v>16.61073324346939</v>
+        <v>16.52802988146939</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1121299285767758</v>
+        <v>0.1127740351182569</v>
       </c>
       <c r="T17">
-        <v>1.11841788681315</v>
+        <v>1.129278448439897</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.1573728393044</v>
+        <v>10.46003703684787</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1012777094993358</v>
+        <v>0.1011066797084122</v>
       </c>
       <c r="C18">
-        <v>174.4435793474744</v>
+        <v>172.8286032694716</v>
       </c>
       <c r="D18">
-        <v>165.9795793474745</v>
+        <v>166.3856032694717</v>
       </c>
       <c r="E18">
-        <v>13.936</v>
+        <v>15.957</v>
       </c>
       <c r="F18">
-        <v>32.336</v>
+        <v>34.357</v>
       </c>
       <c r="G18">
         <v>40.8</v>
@@ -2763,28 +2763,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M18">
-        <v>1.6750048</v>
+        <v>1.7796926</v>
       </c>
       <c r="N18">
-        <v>15.84560744489796</v>
+        <v>15.74091964489796</v>
       </c>
       <c r="O18">
-        <v>3.327577563428572</v>
+        <v>3.305593125428572</v>
       </c>
       <c r="P18">
-        <v>12.51802988146939</v>
+        <v>12.43532651946939</v>
       </c>
       <c r="Q18">
-        <v>16.52802988146939</v>
+        <v>16.44532651946939</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1127740351182569</v>
+        <v>0.1134336622992918</v>
       </c>
       <c r="T18">
-        <v>1.129278448439897</v>
+        <v>1.140400710346807</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.46003703684787</v>
+        <v>9.844740740562703</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1011066797084122</v>
+        <v>0.1011773899174885</v>
       </c>
       <c r="C19">
-        <v>172.8286032694716</v>
+        <v>170.6394969433629</v>
       </c>
       <c r="D19">
-        <v>166.3856032694717</v>
+        <v>166.2174969433629</v>
       </c>
       <c r="E19">
-        <v>15.957</v>
+        <v>17.978</v>
       </c>
       <c r="F19">
-        <v>34.357</v>
+        <v>36.378</v>
       </c>
       <c r="G19">
         <v>40.8</v>
@@ -2845,45 +2845,45 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M19">
-        <v>1.7796926</v>
+        <v>1.946223</v>
       </c>
       <c r="N19">
-        <v>15.74091964489796</v>
+        <v>15.57438924489796</v>
       </c>
       <c r="O19">
-        <v>3.305593125428572</v>
+        <v>3.270621741428572</v>
       </c>
       <c r="P19">
-        <v>12.43532651946939</v>
+        <v>12.30376750346939</v>
       </c>
       <c r="Q19">
-        <v>16.44532651946939</v>
+        <v>16.31376750346939</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1134336622992918</v>
+        <v>0.1141093779481567</v>
       </c>
       <c r="T19">
-        <v>1.140400710346807</v>
+        <v>1.151794246934373</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.21</v>
       </c>
       <c r="W19">
-        <v>0.040922</v>
+        <v>0.042265</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>9.844740740562703</v>
+        <v>9.002366247289217</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1011773899174885</v>
+        <v>0.1010197901265649</v>
       </c>
       <c r="C20">
-        <v>170.6394969433629</v>
+        <v>168.9936406274335</v>
       </c>
       <c r="D20">
-        <v>166.2174969433629</v>
+        <v>166.5926406274336</v>
       </c>
       <c r="E20">
-        <v>17.978</v>
+        <v>19.999</v>
       </c>
       <c r="F20">
-        <v>36.378</v>
+        <v>38.399</v>
       </c>
       <c r="G20">
         <v>40.8</v>
@@ -2927,28 +2927,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M20">
-        <v>1.946223</v>
+        <v>2.0543465</v>
       </c>
       <c r="N20">
-        <v>15.57438924489796</v>
+        <v>15.46626574489796</v>
       </c>
       <c r="O20">
-        <v>3.270621741428572</v>
+        <v>3.247915806428572</v>
       </c>
       <c r="P20">
-        <v>12.30376750346939</v>
+        <v>12.21834993846939</v>
       </c>
       <c r="Q20">
-        <v>16.31376750346939</v>
+        <v>16.22834993846939</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1141093779481567</v>
+        <v>0.1148017779340307</v>
       </c>
       <c r="T20">
-        <v>1.151794246934373</v>
+        <v>1.16346910541299</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.002366247289217</v>
+        <v>8.528557497431891</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1010197901265649</v>
+        <v>0.1008621903356413</v>
       </c>
       <c r="C21">
-        <v>168.9936406274335</v>
+        <v>167.3494814989951</v>
       </c>
       <c r="D21">
-        <v>166.5926406274336</v>
+        <v>166.9694814989951</v>
       </c>
       <c r="E21">
-        <v>19.999</v>
+        <v>22.02</v>
       </c>
       <c r="F21">
-        <v>38.399</v>
+        <v>40.42</v>
       </c>
       <c r="G21">
         <v>40.8</v>
@@ -3009,28 +3009,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M21">
-        <v>2.0543465</v>
+        <v>2.16247</v>
       </c>
       <c r="N21">
-        <v>15.46626574489796</v>
+        <v>15.35814224489796</v>
       </c>
       <c r="O21">
-        <v>3.247915806428572</v>
+        <v>3.225209871428572</v>
       </c>
       <c r="P21">
-        <v>12.21834993846939</v>
+        <v>12.13293237346939</v>
       </c>
       <c r="Q21">
-        <v>16.22834993846939</v>
+        <v>16.14293237346939</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1148017779340307</v>
+        <v>0.1155114879195516</v>
       </c>
       <c r="T21">
-        <v>1.16346910541299</v>
+        <v>1.175435835353573</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.528557497431891</v>
+        <v>8.102129622560296</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1008621903356413</v>
+        <v>0.1007045905447176</v>
       </c>
       <c r="C22">
-        <v>167.3494814989951</v>
+        <v>165.7070311015279</v>
       </c>
       <c r="D22">
-        <v>166.9694814989951</v>
+        <v>167.3480311015279</v>
       </c>
       <c r="E22">
-        <v>22.02</v>
+        <v>24.041</v>
       </c>
       <c r="F22">
-        <v>40.42</v>
+        <v>42.441</v>
       </c>
       <c r="G22">
         <v>40.8</v>
@@ -3091,28 +3091,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M22">
-        <v>2.16247</v>
+        <v>2.2705935</v>
       </c>
       <c r="N22">
-        <v>15.35814224489796</v>
+        <v>15.25001874489796</v>
       </c>
       <c r="O22">
-        <v>3.225209871428572</v>
+        <v>3.202503936428572</v>
       </c>
       <c r="P22">
-        <v>12.13293237346939</v>
+        <v>12.04751480846939</v>
       </c>
       <c r="Q22">
-        <v>16.14293237346939</v>
+        <v>16.05751480846939</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1155114879195516</v>
+        <v>0.116239165246478</v>
       </c>
       <c r="T22">
-        <v>1.175435835353573</v>
+        <v>1.187705520482524</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.102129622560296</v>
+        <v>7.7163139262479</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1007045905447176</v>
+        <v>0.100686030753794</v>
       </c>
       <c r="C23">
-        <v>165.7070311015279</v>
+        <v>163.7307241229479</v>
       </c>
       <c r="D23">
-        <v>167.3480311015279</v>
+        <v>167.392724122948</v>
       </c>
       <c r="E23">
-        <v>24.041</v>
+        <v>26.062</v>
       </c>
       <c r="F23">
-        <v>42.441</v>
+        <v>44.462</v>
       </c>
       <c r="G23">
         <v>40.8</v>
@@ -3173,45 +3173,45 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M23">
-        <v>2.270593499999999</v>
+        <v>2.4142866</v>
       </c>
       <c r="N23">
-        <v>15.25001874489796</v>
+        <v>15.10632564489796</v>
       </c>
       <c r="O23">
-        <v>3.202503936428572</v>
+        <v>3.172328385428572</v>
       </c>
       <c r="P23">
-        <v>12.04751480846939</v>
+        <v>11.93399725946939</v>
       </c>
       <c r="Q23">
-        <v>16.05751480846939</v>
+        <v>15.94399725946939</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.116239165246478</v>
+        <v>0.1169855009664025</v>
       </c>
       <c r="T23">
-        <v>1.187705520482524</v>
+        <v>1.200289812922475</v>
       </c>
       <c r="U23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.21</v>
       </c>
       <c r="W23">
-        <v>0.042265</v>
+        <v>0.042897</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>7.716313926247901</v>
+        <v>7.257055663937314</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.100686030753794</v>
+        <v>0.1005347509628703</v>
       </c>
       <c r="C24">
-        <v>163.7307241229479</v>
+        <v>162.0749066105126</v>
       </c>
       <c r="D24">
-        <v>167.392724122948</v>
+        <v>167.7579066105126</v>
       </c>
       <c r="E24">
-        <v>26.062</v>
+        <v>28.08300000000001</v>
       </c>
       <c r="F24">
-        <v>44.462</v>
+        <v>46.483</v>
       </c>
       <c r="G24">
         <v>40.8</v>
@@ -3255,28 +3255,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M24">
-        <v>2.4142866</v>
+        <v>2.5240269</v>
       </c>
       <c r="N24">
-        <v>15.10632564489796</v>
+        <v>14.99658534489796</v>
       </c>
       <c r="O24">
-        <v>3.172328385428572</v>
+        <v>3.149282922428572</v>
       </c>
       <c r="P24">
-        <v>11.93399725946939</v>
+        <v>11.84730242246939</v>
       </c>
       <c r="Q24">
-        <v>15.94399725946939</v>
+        <v>15.85730242246939</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1169855009664025</v>
+        <v>0.1177512220297017</v>
       </c>
       <c r="T24">
-        <v>1.200289812922475</v>
+        <v>1.213200970101125</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.257055663937314</v>
+        <v>6.941531504635691</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1005347509628703</v>
+        <v>0.1003834711719467</v>
       </c>
       <c r="C25">
-        <v>162.0749066105126</v>
+        <v>160.4206859395073</v>
       </c>
       <c r="D25">
-        <v>167.7579066105126</v>
+        <v>168.1246859395073</v>
       </c>
       <c r="E25">
-        <v>28.08300000000001</v>
+        <v>30.10400000000001</v>
       </c>
       <c r="F25">
-        <v>46.483</v>
+        <v>48.504</v>
       </c>
       <c r="G25">
         <v>40.8</v>
@@ -3337,28 +3337,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M25">
-        <v>2.5240269</v>
+        <v>2.6337672</v>
       </c>
       <c r="N25">
-        <v>14.99658534489796</v>
+        <v>14.88684504489796</v>
       </c>
       <c r="O25">
-        <v>3.149282922428572</v>
+        <v>3.126237459428571</v>
       </c>
       <c r="P25">
-        <v>11.84730242246939</v>
+        <v>11.76060758546939</v>
       </c>
       <c r="Q25">
-        <v>15.85730242246939</v>
+        <v>15.77060758546939</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1177512220297017</v>
+        <v>0.1185370936472983</v>
       </c>
       <c r="T25">
-        <v>1.213200970101125</v>
+        <v>1.226451894573951</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.941531504635691</v>
+        <v>6.652301025275871</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1003834711719467</v>
+        <v>0.100232191381023</v>
       </c>
       <c r="C26">
-        <v>160.4206859395073</v>
+        <v>158.7680726066969</v>
       </c>
       <c r="D26">
-        <v>168.1246859395073</v>
+        <v>168.4930726066969</v>
       </c>
       <c r="E26">
-        <v>30.104</v>
+        <v>32.125</v>
       </c>
       <c r="F26">
-        <v>48.504</v>
+        <v>50.525</v>
       </c>
       <c r="G26">
         <v>40.8</v>
@@ -3419,28 +3419,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M26">
-        <v>2.6337672</v>
+        <v>2.7435075</v>
       </c>
       <c r="N26">
-        <v>14.88684504489796</v>
+        <v>14.77710474489796</v>
       </c>
       <c r="O26">
-        <v>3.126237459428572</v>
+        <v>3.103191996428572</v>
       </c>
       <c r="P26">
-        <v>11.76060758546939</v>
+        <v>11.67391274846939</v>
       </c>
       <c r="Q26">
-        <v>15.77060758546939</v>
+        <v>15.68391274846939</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1185370936472983</v>
+        <v>0.1193439218413641</v>
       </c>
       <c r="T26">
-        <v>1.226451894573951</v>
+        <v>1.240056177032718</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.652301025275872</v>
+        <v>6.386208984264838</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.100232191381023</v>
+        <v>0.1000809115900994</v>
       </c>
       <c r="C27">
-        <v>158.7680726066969</v>
+        <v>157.1170772010481</v>
       </c>
       <c r="D27">
-        <v>168.4930726066969</v>
+        <v>168.8630772010481</v>
       </c>
       <c r="E27">
-        <v>32.125</v>
+        <v>34.146</v>
       </c>
       <c r="F27">
-        <v>50.525</v>
+        <v>52.546</v>
       </c>
       <c r="G27">
         <v>40.8</v>
@@ -3501,28 +3501,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M27">
-        <v>2.7435075</v>
+        <v>2.8532478</v>
       </c>
       <c r="N27">
-        <v>14.77710474489796</v>
+        <v>14.66736444489796</v>
       </c>
       <c r="O27">
-        <v>3.103191996428572</v>
+        <v>3.080146533428572</v>
       </c>
       <c r="P27">
-        <v>11.67391274846939</v>
+        <v>11.58721791146939</v>
       </c>
       <c r="Q27">
-        <v>15.68391274846939</v>
+        <v>15.59721791146939</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1193439218413641</v>
+        <v>0.120172556202837</v>
       </c>
       <c r="T27">
-        <v>1.240056177032718</v>
+        <v>1.254028142801182</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.386208984264838</v>
+        <v>6.140585561793112</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1000809115900994</v>
+        <v>0.1001429317991758</v>
       </c>
       <c r="C28">
-        <v>157.1170772010481</v>
+        <v>154.9441899697237</v>
       </c>
       <c r="D28">
-        <v>168.8630772010481</v>
+        <v>168.7111899697237</v>
       </c>
       <c r="E28">
-        <v>34.146</v>
+        <v>36.167</v>
       </c>
       <c r="F28">
-        <v>52.546</v>
+        <v>54.567</v>
       </c>
       <c r="G28">
         <v>40.8</v>
@@ -3583,45 +3583,45 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M28">
-        <v>2.8532478</v>
+        <v>3.0175551</v>
       </c>
       <c r="N28">
-        <v>14.66736444489796</v>
+        <v>14.50305714489796</v>
       </c>
       <c r="O28">
-        <v>3.080146533428572</v>
+        <v>3.045642000428572</v>
       </c>
       <c r="P28">
-        <v>11.58721791146939</v>
+        <v>11.45741514446939</v>
       </c>
       <c r="Q28">
-        <v>15.59721791146939</v>
+        <v>15.46741514446939</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.120172556202837</v>
+        <v>0.1210238928755832</v>
       </c>
       <c r="T28">
-        <v>1.254028142801182</v>
+        <v>1.268382902152344</v>
       </c>
       <c r="U28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.21</v>
       </c>
       <c r="W28">
-        <v>0.042897</v>
+        <v>0.043687</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>6.140585561793112</v>
+        <v>5.806227778540966</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1001429317991758</v>
+        <v>0.09999955200825213</v>
       </c>
       <c r="C29">
-        <v>154.9441899697237</v>
+        <v>153.2747416603726</v>
       </c>
       <c r="D29">
-        <v>168.7111899697237</v>
+        <v>169.0627416603726</v>
       </c>
       <c r="E29">
-        <v>36.167</v>
+        <v>38.188</v>
       </c>
       <c r="F29">
-        <v>54.567</v>
+        <v>56.588</v>
       </c>
       <c r="G29">
         <v>40.8</v>
@@ -3665,28 +3665,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M29">
-        <v>3.0175551</v>
+        <v>3.1293164</v>
       </c>
       <c r="N29">
-        <v>14.50305714489796</v>
+        <v>14.39129584489796</v>
       </c>
       <c r="O29">
-        <v>3.045642000428572</v>
+        <v>3.022172127428572</v>
       </c>
       <c r="P29">
-        <v>11.45741514446939</v>
+        <v>11.36912371746939</v>
       </c>
       <c r="Q29">
-        <v>15.46741514446939</v>
+        <v>15.37912371746939</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1210238928755832</v>
+        <v>0.1218988777892391</v>
       </c>
       <c r="T29">
-        <v>1.268382902152344</v>
+        <v>1.283136404818815</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.806227778540966</v>
+        <v>5.598862500735931</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09999955200825213</v>
+        <v>0.0998561722173285</v>
       </c>
       <c r="C30">
-        <v>153.2747416603726</v>
+        <v>151.6067615008994</v>
       </c>
       <c r="D30">
-        <v>169.0627416603726</v>
+        <v>169.4157615008994</v>
       </c>
       <c r="E30">
-        <v>38.188</v>
+        <v>40.20900000000001</v>
       </c>
       <c r="F30">
-        <v>56.588</v>
+        <v>58.60900000000001</v>
       </c>
       <c r="G30">
         <v>40.8</v>
@@ -3747,28 +3747,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M30">
-        <v>3.1293164</v>
+        <v>3.2410777</v>
       </c>
       <c r="N30">
-        <v>14.39129584489796</v>
+        <v>14.27953454489796</v>
       </c>
       <c r="O30">
-        <v>3.022172127428572</v>
+        <v>2.998702254428572</v>
       </c>
       <c r="P30">
-        <v>11.36912371746939</v>
+        <v>11.28083229046939</v>
       </c>
       <c r="Q30">
-        <v>15.37912371746939</v>
+        <v>15.29083229046939</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1218988777892391</v>
+        <v>0.1227985101652514</v>
       </c>
       <c r="T30">
-        <v>1.283136404818815</v>
+        <v>1.298305499109695</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.598862500735931</v>
+        <v>5.405798276572622</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0998561722173285</v>
+        <v>0.09971279242640484</v>
       </c>
       <c r="C31">
-        <v>151.6067615008994</v>
+        <v>149.9402587074779</v>
       </c>
       <c r="D31">
-        <v>169.4157615008994</v>
+        <v>169.7702587074779</v>
       </c>
       <c r="E31">
-        <v>40.209</v>
+        <v>42.23</v>
       </c>
       <c r="F31">
-        <v>58.60899999999999</v>
+        <v>60.63</v>
       </c>
       <c r="G31">
         <v>40.8</v>
@@ -3829,28 +3829,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M31">
-        <v>3.2410777</v>
+        <v>3.352839</v>
       </c>
       <c r="N31">
-        <v>14.27953454489796</v>
+        <v>14.16777324489796</v>
       </c>
       <c r="O31">
-        <v>2.998702254428572</v>
+        <v>2.975232381428572</v>
       </c>
       <c r="P31">
-        <v>11.28083229046939</v>
+        <v>11.19254086346939</v>
       </c>
       <c r="Q31">
-        <v>15.29083229046939</v>
+        <v>15.20254086346939</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1227985101652514</v>
+        <v>0.1237238463234355</v>
       </c>
       <c r="T31">
-        <v>1.298305499109695</v>
+        <v>1.313907996094599</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.405798276572623</v>
+        <v>5.225605000686869</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09971279242640484</v>
+        <v>0.09956941263548122</v>
       </c>
       <c r="C32">
-        <v>149.9402587074779</v>
+        <v>148.2752425735818</v>
       </c>
       <c r="D32">
-        <v>169.7702587074779</v>
+        <v>170.1262425735818</v>
       </c>
       <c r="E32">
-        <v>42.23</v>
+        <v>44.251</v>
       </c>
       <c r="F32">
-        <v>60.63</v>
+        <v>62.651</v>
       </c>
       <c r="G32">
         <v>40.8</v>
@@ -3911,28 +3911,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M32">
-        <v>3.352839</v>
+        <v>3.4646003</v>
       </c>
       <c r="N32">
-        <v>14.16777324489796</v>
+        <v>14.05601194489796</v>
       </c>
       <c r="O32">
-        <v>2.975232381428572</v>
+        <v>2.951762508428572</v>
       </c>
       <c r="P32">
-        <v>11.19254086346939</v>
+        <v>11.10424943646939</v>
       </c>
       <c r="Q32">
-        <v>15.20254086346939</v>
+        <v>15.11424943646939</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1237238463234355</v>
+        <v>0.124676003819538</v>
       </c>
       <c r="T32">
-        <v>1.313907996094599</v>
+        <v>1.329962739368921</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.225605000686869</v>
+        <v>5.057037097438905</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09956941263548122</v>
+        <v>0.09942603284455757</v>
       </c>
       <c r="C33">
-        <v>148.2752425735818</v>
+        <v>146.611722470797</v>
       </c>
       <c r="D33">
-        <v>170.1262425735818</v>
+        <v>170.483722470797</v>
       </c>
       <c r="E33">
-        <v>44.251</v>
+        <v>46.272</v>
       </c>
       <c r="F33">
-        <v>62.651</v>
+        <v>64.672</v>
       </c>
       <c r="G33">
         <v>40.8</v>
@@ -3993,28 +3993,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M33">
-        <v>3.4646003</v>
+        <v>3.5763616</v>
       </c>
       <c r="N33">
-        <v>14.05601194489796</v>
+        <v>13.94425064489796</v>
       </c>
       <c r="O33">
-        <v>2.951762508428572</v>
+        <v>2.928292635428572</v>
       </c>
       <c r="P33">
-        <v>11.10424943646939</v>
+        <v>11.01595800946939</v>
       </c>
       <c r="Q33">
-        <v>15.11424943646939</v>
+        <v>15.02595800946939</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.124676003819538</v>
+        <v>0.1256561659478788</v>
       </c>
       <c r="T33">
-        <v>1.329962739368921</v>
+        <v>1.34648968097484</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.057037097438905</v>
+        <v>4.89900468814394</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09942603284455757</v>
+        <v>0.09928265305363393</v>
       </c>
       <c r="C34">
-        <v>146.611722470797</v>
+        <v>144.9497078496438</v>
       </c>
       <c r="D34">
-        <v>170.483722470797</v>
+        <v>170.8427078496438</v>
       </c>
       <c r="E34">
-        <v>46.272</v>
+        <v>48.293</v>
       </c>
       <c r="F34">
-        <v>64.672</v>
+        <v>66.693</v>
       </c>
       <c r="G34">
         <v>40.8</v>
@@ -4075,28 +4075,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M34">
-        <v>3.5763616</v>
+        <v>3.6881229</v>
       </c>
       <c r="N34">
-        <v>13.94425064489796</v>
+        <v>13.83248934489796</v>
       </c>
       <c r="O34">
-        <v>2.928292635428572</v>
+        <v>2.904822762428572</v>
       </c>
       <c r="P34">
-        <v>11.01595800946939</v>
+        <v>10.92766658246939</v>
       </c>
       <c r="Q34">
-        <v>15.02595800946939</v>
+        <v>14.93766658246939</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1256561659478788</v>
+        <v>0.1266655866472148</v>
       </c>
       <c r="T34">
-        <v>1.34648968097484</v>
+        <v>1.363509964121235</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.89900468814394</v>
+        <v>4.750550000624426</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09928265305363393</v>
+        <v>0.0991392732627103</v>
       </c>
       <c r="C35">
-        <v>144.9497078496438</v>
+        <v>143.2892082404098</v>
       </c>
       <c r="D35">
-        <v>170.8427078496438</v>
+        <v>171.2032082404098</v>
       </c>
       <c r="E35">
-        <v>48.293</v>
+        <v>50.314</v>
       </c>
       <c r="F35">
-        <v>66.693</v>
+        <v>68.714</v>
       </c>
       <c r="G35">
         <v>40.8</v>
@@ -4157,28 +4157,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M35">
-        <v>3.6881229</v>
+        <v>3.7998842</v>
       </c>
       <c r="N35">
-        <v>13.83248934489796</v>
+        <v>13.72072804489796</v>
       </c>
       <c r="O35">
-        <v>2.904822762428572</v>
+        <v>2.881352889428571</v>
       </c>
       <c r="P35">
-        <v>10.92766658246939</v>
+        <v>10.83937515546939</v>
       </c>
       <c r="Q35">
-        <v>14.93766658246939</v>
+        <v>14.84937515546939</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1266655866472148</v>
+        <v>0.1277055958525914</v>
       </c>
       <c r="T35">
-        <v>1.363509964121235</v>
+        <v>1.381046013423581</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.750550000624426</v>
+        <v>4.610827941782532</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0991392732627103</v>
+        <v>0.09968714347178664</v>
       </c>
       <c r="C36">
-        <v>143.2892082404098</v>
+        <v>139.898830570159</v>
       </c>
       <c r="D36">
-        <v>171.2032082404098</v>
+        <v>169.833830570159</v>
       </c>
       <c r="E36">
-        <v>50.314</v>
+        <v>52.335</v>
       </c>
       <c r="F36">
-        <v>68.714</v>
+        <v>70.735</v>
       </c>
       <c r="G36">
         <v>40.8</v>
@@ -4239,45 +4239,45 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M36">
-        <v>3.7998842</v>
+        <v>4.088483</v>
       </c>
       <c r="N36">
-        <v>13.72072804489796</v>
+        <v>13.43212924489796</v>
       </c>
       <c r="O36">
-        <v>2.881352889428571</v>
+        <v>2.820747141428572</v>
       </c>
       <c r="P36">
-        <v>10.83937515546939</v>
+        <v>10.61138210346939</v>
       </c>
       <c r="Q36">
-        <v>14.84937515546939</v>
+        <v>14.62138210346939</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1277055958525914</v>
+        <v>0.1287776053412102</v>
       </c>
       <c r="T36">
-        <v>1.381046013423581</v>
+        <v>1.399121633473692</v>
       </c>
       <c r="U36">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V36">
         <v>0.21</v>
       </c>
       <c r="W36">
-        <v>0.043687</v>
+        <v>0.04566200000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.610827941782532</v>
+        <v>4.285357734127293</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09968714347178664</v>
+        <v>0.09956351368086303</v>
       </c>
       <c r="C37">
-        <v>139.898830570159</v>
+        <v>138.1849204962505</v>
       </c>
       <c r="D37">
-        <v>169.833830570159</v>
+        <v>170.1409204962505</v>
       </c>
       <c r="E37">
-        <v>52.335</v>
+        <v>54.356</v>
       </c>
       <c r="F37">
-        <v>70.735</v>
+        <v>72.756</v>
       </c>
       <c r="G37">
         <v>40.8</v>
@@ -4321,28 +4321,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M37">
-        <v>4.088483</v>
+        <v>4.2052968</v>
       </c>
       <c r="N37">
-        <v>13.43212924489796</v>
+        <v>13.31531544489796</v>
       </c>
       <c r="O37">
-        <v>2.820747141428572</v>
+        <v>2.796216243428572</v>
       </c>
       <c r="P37">
-        <v>10.61138210346939</v>
+        <v>10.51909920146939</v>
       </c>
       <c r="Q37">
-        <v>14.62138210346939</v>
+        <v>14.52909920146939</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1287776053412102</v>
+        <v>0.1298831151263485</v>
       </c>
       <c r="T37">
-        <v>1.399121633473692</v>
+        <v>1.417762116650369</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.285357734127293</v>
+        <v>4.166320019290424</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09956351368086301</v>
+        <v>0.09943988388993938</v>
       </c>
       <c r="C38">
-        <v>138.1849204962506</v>
+        <v>136.472122981014</v>
       </c>
       <c r="D38">
-        <v>170.1409204962505</v>
+        <v>170.4491229810139</v>
       </c>
       <c r="E38">
-        <v>54.356</v>
+        <v>56.377</v>
       </c>
       <c r="F38">
-        <v>72.756</v>
+        <v>74.777</v>
       </c>
       <c r="G38">
         <v>40.8</v>
@@ -4403,28 +4403,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M38">
-        <v>4.2052968</v>
+        <v>4.3221106</v>
       </c>
       <c r="N38">
-        <v>13.31531544489796</v>
+        <v>13.19850164489796</v>
       </c>
       <c r="O38">
-        <v>2.796216243428572</v>
+        <v>2.771685345428572</v>
       </c>
       <c r="P38">
-        <v>10.51909920146939</v>
+        <v>10.42681629946939</v>
       </c>
       <c r="Q38">
-        <v>14.52909920146939</v>
+        <v>14.43681629946939</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1298831151263485</v>
+        <v>0.1310237204602212</v>
       </c>
       <c r="T38">
-        <v>1.417762116650368</v>
+        <v>1.436994361197733</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.166320019290424</v>
+        <v>4.053716775525818</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09943988388993938</v>
+        <v>0.1003669540990157</v>
       </c>
       <c r="C39">
-        <v>136.472122981014</v>
+        <v>132.1668288811488</v>
       </c>
       <c r="D39">
-        <v>170.4491229810139</v>
+        <v>168.1648288811488</v>
       </c>
       <c r="E39">
-        <v>56.377</v>
+        <v>58.398</v>
       </c>
       <c r="F39">
-        <v>74.777</v>
+        <v>76.798</v>
       </c>
       <c r="G39">
         <v>40.8</v>
@@ -4485,45 +4485,45 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M39">
-        <v>4.3221106</v>
+        <v>4.7077174</v>
       </c>
       <c r="N39">
-        <v>13.19850164489796</v>
+        <v>12.81289484489796</v>
       </c>
       <c r="O39">
-        <v>2.771685345428572</v>
+        <v>2.690707917428572</v>
       </c>
       <c r="P39">
-        <v>10.42681629946939</v>
+        <v>10.12218692746939</v>
       </c>
       <c r="Q39">
-        <v>14.43681629946939</v>
+        <v>14.13218692746939</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1310237204602212</v>
+        <v>0.1322011195145415</v>
       </c>
       <c r="T39">
-        <v>1.436994361197733</v>
+        <v>1.456847000730497</v>
       </c>
       <c r="U39">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V39">
         <v>0.21</v>
       </c>
       <c r="W39">
-        <v>0.04566200000000001</v>
+        <v>0.048427</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.053716775525818</v>
+        <v>3.721678842680311</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1003669540990157</v>
+        <v>0.1002709743080921</v>
       </c>
       <c r="C40">
-        <v>132.1668288811488</v>
+        <v>130.3794771571823</v>
       </c>
       <c r="D40">
-        <v>168.1648288811488</v>
+        <v>168.3984771571823</v>
       </c>
       <c r="E40">
-        <v>58.398</v>
+        <v>60.419</v>
       </c>
       <c r="F40">
-        <v>76.798</v>
+        <v>78.819</v>
       </c>
       <c r="G40">
         <v>40.8</v>
@@ -4567,28 +4567,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M40">
-        <v>4.7077174</v>
+        <v>4.8316047</v>
       </c>
       <c r="N40">
-        <v>12.81289484489796</v>
+        <v>12.68900754489796</v>
       </c>
       <c r="O40">
-        <v>2.690707917428572</v>
+        <v>2.664691584428572</v>
       </c>
       <c r="P40">
-        <v>10.12218692746939</v>
+        <v>10.02431596046939</v>
       </c>
       <c r="Q40">
-        <v>14.13218692746939</v>
+        <v>14.03431596046939</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1322011195145415</v>
+        <v>0.1334171218165444</v>
       </c>
       <c r="T40">
-        <v>1.456847000730497</v>
+        <v>1.477350546477449</v>
       </c>
       <c r="U40">
         <v>0.0613</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.721678842680311</v>
+        <v>3.626251180047483</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1002709743080921</v>
+        <v>0.1001749945171685</v>
       </c>
       <c r="C41">
-        <v>130.3794771571823</v>
+        <v>128.5927755985595</v>
       </c>
       <c r="D41">
-        <v>168.3984771571823</v>
+        <v>168.6327755985595</v>
       </c>
       <c r="E41">
-        <v>60.419</v>
+        <v>62.44</v>
       </c>
       <c r="F41">
-        <v>78.819</v>
+        <v>80.84</v>
       </c>
       <c r="G41">
         <v>40.8</v>
@@ -4649,28 +4649,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M41">
-        <v>4.8316047</v>
+        <v>4.955492</v>
       </c>
       <c r="N41">
-        <v>12.68900754489796</v>
+        <v>12.56512024489796</v>
       </c>
       <c r="O41">
-        <v>2.664691584428572</v>
+        <v>2.638675251428572</v>
       </c>
       <c r="P41">
-        <v>10.02431596046939</v>
+        <v>9.92644499346939</v>
       </c>
       <c r="Q41">
-        <v>14.03431596046939</v>
+        <v>13.93644499346939</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1334171218165444</v>
+        <v>0.1346736575286141</v>
       </c>
       <c r="T41">
-        <v>1.477350546477449</v>
+        <v>1.498537543749301</v>
       </c>
       <c r="U41">
         <v>0.0613</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.626251180047483</v>
+        <v>3.535594900546295</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1001749945171685</v>
+        <v>0.1009859347262448</v>
       </c>
       <c r="C42">
-        <v>128.5927755985595</v>
+        <v>124.6124496105072</v>
       </c>
       <c r="D42">
-        <v>168.6327755985595</v>
+        <v>166.6734496105072</v>
       </c>
       <c r="E42">
-        <v>62.44</v>
+        <v>64.46100000000001</v>
       </c>
       <c r="F42">
-        <v>80.84</v>
+        <v>82.861</v>
       </c>
       <c r="G42">
         <v>40.8</v>
@@ -4731,45 +4731,45 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M42">
-        <v>4.955492</v>
+        <v>5.311390100000001</v>
       </c>
       <c r="N42">
-        <v>12.56512024489796</v>
+        <v>12.20922214489796</v>
       </c>
       <c r="O42">
-        <v>2.638675251428572</v>
+        <v>2.563936650428572</v>
       </c>
       <c r="P42">
-        <v>9.92644499346939</v>
+        <v>9.645285494469389</v>
       </c>
       <c r="Q42">
-        <v>13.93644499346939</v>
+        <v>13.65528549446939</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1346736575286141</v>
+        <v>0.1359727876716014</v>
       </c>
       <c r="T42">
-        <v>1.498537543749301</v>
+        <v>1.520442744318502</v>
       </c>
       <c r="U42">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V42">
         <v>0.21</v>
       </c>
       <c r="W42">
-        <v>0.048427</v>
+        <v>0.050639</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.535594900546295</v>
+        <v>3.298686768440894</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1009859347262448</v>
+        <v>0.1009120749353212</v>
       </c>
       <c r="C43">
-        <v>124.6124496105072</v>
+        <v>122.7680168815509</v>
       </c>
       <c r="D43">
-        <v>166.6734496105072</v>
+        <v>166.8500168815509</v>
       </c>
       <c r="E43">
-        <v>64.46100000000001</v>
+        <v>66.482</v>
       </c>
       <c r="F43">
-        <v>82.861</v>
+        <v>84.88200000000001</v>
       </c>
       <c r="G43">
         <v>40.8</v>
@@ -4813,28 +4813,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M43">
-        <v>5.311390100000001</v>
+        <v>5.4409362</v>
       </c>
       <c r="N43">
-        <v>12.20922214489796</v>
+        <v>12.07967604489796</v>
       </c>
       <c r="O43">
-        <v>2.563936650428572</v>
+        <v>2.536731969428572</v>
       </c>
       <c r="P43">
-        <v>9.645285494469389</v>
+        <v>9.542944075469389</v>
       </c>
       <c r="Q43">
-        <v>13.65528549446939</v>
+        <v>13.55294407546939</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1359727876716014</v>
+        <v>0.1373167154057262</v>
       </c>
       <c r="T43">
-        <v>1.520442744318502</v>
+        <v>1.54310329663147</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.298686768440894</v>
+        <v>3.22014660728754</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1009120749353212</v>
+        <v>0.1008382151443975</v>
       </c>
       <c r="C44">
-        <v>122.7680168815509</v>
+        <v>120.923958646108</v>
       </c>
       <c r="D44">
-        <v>166.8500168815509</v>
+        <v>167.026958646108</v>
       </c>
       <c r="E44">
-        <v>66.482</v>
+        <v>68.50299999999999</v>
       </c>
       <c r="F44">
-        <v>84.88199999999999</v>
+        <v>86.90299999999999</v>
       </c>
       <c r="G44">
         <v>40.8</v>
@@ -4895,28 +4895,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M44">
-        <v>5.440936199999999</v>
+        <v>5.5704823</v>
       </c>
       <c r="N44">
-        <v>12.07967604489796</v>
+        <v>11.95012994489796</v>
       </c>
       <c r="O44">
-        <v>2.536731969428572</v>
+        <v>2.509527288428572</v>
       </c>
       <c r="P44">
-        <v>9.542944075469389</v>
+        <v>9.440602656469389</v>
       </c>
       <c r="Q44">
-        <v>13.55294407546939</v>
+        <v>13.45060265646939</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1373167154057262</v>
+        <v>0.138707798498943</v>
       </c>
       <c r="T44">
-        <v>1.54310329663147</v>
+        <v>1.566558956043138</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.22014660728754</v>
+        <v>3.145259476885504</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1008382151443975</v>
+        <v>0.1007643553534739</v>
       </c>
       <c r="C45">
-        <v>120.923958646108</v>
+        <v>119.0802760968761</v>
       </c>
       <c r="D45">
-        <v>167.026958646108</v>
+        <v>167.2042760968762</v>
       </c>
       <c r="E45">
-        <v>68.50299999999999</v>
+        <v>70.524</v>
       </c>
       <c r="F45">
-        <v>86.90299999999999</v>
+        <v>88.92399999999999</v>
       </c>
       <c r="G45">
         <v>40.8</v>
@@ -4977,28 +4977,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M45">
-        <v>5.5704823</v>
+        <v>5.7000284</v>
       </c>
       <c r="N45">
-        <v>11.95012994489796</v>
+        <v>11.82058384489796</v>
       </c>
       <c r="O45">
-        <v>2.509527288428572</v>
+        <v>2.482322607428572</v>
       </c>
       <c r="P45">
-        <v>9.440602656469389</v>
+        <v>9.338261237469389</v>
       </c>
       <c r="Q45">
-        <v>13.45060265646939</v>
+        <v>13.34826123746939</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.138707798498943</v>
+        <v>0.1401485631312034</v>
       </c>
       <c r="T45">
-        <v>1.566558956043138</v>
+        <v>1.590852317576651</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.145259476885504</v>
+        <v>3.073776306956288</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1007643553534739</v>
+        <v>0.1006904955625503</v>
       </c>
       <c r="C46">
-        <v>119.0802760968761</v>
+        <v>117.2369704316235</v>
       </c>
       <c r="D46">
-        <v>167.2042760968762</v>
+        <v>167.3819704316235</v>
       </c>
       <c r="E46">
-        <v>70.524</v>
+        <v>72.54499999999999</v>
       </c>
       <c r="F46">
-        <v>88.92399999999999</v>
+        <v>90.94499999999999</v>
       </c>
       <c r="G46">
         <v>40.8</v>
@@ -5059,28 +5059,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M46">
-        <v>5.7000284</v>
+        <v>5.8295745</v>
       </c>
       <c r="N46">
-        <v>11.82058384489796</v>
+        <v>11.69103774489796</v>
       </c>
       <c r="O46">
-        <v>2.482322607428572</v>
+        <v>2.455117926428572</v>
       </c>
       <c r="P46">
-        <v>9.338261237469389</v>
+        <v>9.235919818469389</v>
       </c>
       <c r="Q46">
-        <v>13.34826123746939</v>
+        <v>13.24591981846939</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1401485631312034</v>
+        <v>0.1416417192046368</v>
       </c>
       <c r="T46">
-        <v>1.590852317576651</v>
+        <v>1.61602907407502</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.073776306956288</v>
+        <v>3.005470166801704</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1006904955625503</v>
+        <v>0.1034511557716266</v>
       </c>
       <c r="C47">
-        <v>117.2369704316235</v>
+        <v>108.8212357978547</v>
       </c>
       <c r="D47">
-        <v>167.3819704316235</v>
+        <v>160.9872357978547</v>
       </c>
       <c r="E47">
-        <v>72.54499999999999</v>
+        <v>74.566</v>
       </c>
       <c r="F47">
-        <v>90.94499999999999</v>
+        <v>92.96600000000001</v>
       </c>
       <c r="G47">
         <v>40.8</v>
@@ -5141,45 +5141,45 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M47">
-        <v>5.8295745</v>
+        <v>6.684255400000001</v>
       </c>
       <c r="N47">
-        <v>11.69103774489796</v>
+        <v>10.83635684489796</v>
       </c>
       <c r="O47">
-        <v>2.455117926428572</v>
+        <v>2.275634937428571</v>
       </c>
       <c r="P47">
-        <v>9.235919818469389</v>
+        <v>8.560721907469389</v>
       </c>
       <c r="Q47">
-        <v>13.24591981846939</v>
+        <v>12.57072190746939</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1416417192046368</v>
+        <v>0.1431901773548641</v>
       </c>
       <c r="T47">
-        <v>1.61602907407502</v>
+        <v>1.642138303036291</v>
       </c>
       <c r="U47">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V47">
         <v>0.21</v>
       </c>
       <c r="W47">
-        <v>0.050639</v>
+        <v>0.056801</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.005470166801704</v>
+        <v>2.621176360929889</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1034511557716266</v>
+        <v>0.103438915980703</v>
       </c>
       <c r="C48">
-        <v>108.8212357978547</v>
+        <v>106.8275092371271</v>
       </c>
       <c r="D48">
-        <v>160.9872357978547</v>
+        <v>161.0145092371271</v>
       </c>
       <c r="E48">
-        <v>74.566</v>
+        <v>76.58700000000002</v>
       </c>
       <c r="F48">
-        <v>92.96600000000001</v>
+        <v>94.98700000000001</v>
       </c>
       <c r="G48">
         <v>40.8</v>
@@ -5223,28 +5223,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M48">
-        <v>6.684255400000001</v>
+        <v>6.829565300000001</v>
       </c>
       <c r="N48">
-        <v>10.83635684489796</v>
+        <v>10.69104694489796</v>
       </c>
       <c r="O48">
-        <v>2.275634937428571</v>
+        <v>2.245119858428571</v>
       </c>
       <c r="P48">
-        <v>8.560721907469389</v>
+        <v>8.445927086469387</v>
       </c>
       <c r="Q48">
-        <v>12.57072190746939</v>
+        <v>12.45592708646939</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1431901773548641</v>
+        <v>0.1447970678881188</v>
       </c>
       <c r="T48">
-        <v>1.642138303036291</v>
+        <v>1.669232785920629</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.621176360929889</v>
+        <v>2.56540665112287</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.103438915980703</v>
+        <v>0.1034266761897794</v>
       </c>
       <c r="C49">
-        <v>106.8275092371271</v>
+        <v>104.8337919189525</v>
       </c>
       <c r="D49">
-        <v>161.0145092371271</v>
+        <v>161.0417919189525</v>
       </c>
       <c r="E49">
-        <v>76.58700000000002</v>
+        <v>78.608</v>
       </c>
       <c r="F49">
-        <v>94.98700000000001</v>
+        <v>97.00800000000001</v>
       </c>
       <c r="G49">
         <v>40.8</v>
@@ -5305,28 +5305,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M49">
-        <v>6.829565300000001</v>
+        <v>6.974875200000001</v>
       </c>
       <c r="N49">
-        <v>10.69104694489796</v>
+        <v>10.54573704489796</v>
       </c>
       <c r="O49">
-        <v>2.245119858428571</v>
+        <v>2.214604779428571</v>
       </c>
       <c r="P49">
-        <v>8.445927086469387</v>
+        <v>8.331132265469389</v>
       </c>
       <c r="Q49">
-        <v>12.45592708646939</v>
+        <v>12.34113226546939</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1447970678881188</v>
+        <v>0.1464657619034218</v>
       </c>
       <c r="T49">
-        <v>1.669232785920629</v>
+        <v>1.697369364300518</v>
       </c>
       <c r="U49">
         <v>0.07190000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.56540665112287</v>
+        <v>2.511960679224477</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1034266761897794</v>
+        <v>0.1049241263988557</v>
       </c>
       <c r="C50">
-        <v>104.8337919189525</v>
+        <v>99.54218667248267</v>
       </c>
       <c r="D50">
-        <v>161.0417919189525</v>
+        <v>157.7711866724827</v>
       </c>
       <c r="E50">
-        <v>78.608</v>
+        <v>80.62899999999999</v>
       </c>
       <c r="F50">
-        <v>97.008</v>
+        <v>99.029</v>
       </c>
       <c r="G50">
         <v>40.8</v>
@@ -5387,45 +5387,45 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M50">
-        <v>6.9748752</v>
+        <v>7.5063982</v>
       </c>
       <c r="N50">
-        <v>10.54573704489796</v>
+        <v>10.01421404489796</v>
       </c>
       <c r="O50">
-        <v>2.214604779428572</v>
+        <v>2.102984949428572</v>
       </c>
       <c r="P50">
-        <v>8.331132265469389</v>
+        <v>7.911229095469389</v>
       </c>
       <c r="Q50">
-        <v>12.34113226546939</v>
+        <v>11.92122909546939</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1464657619034218</v>
+        <v>0.148199894899717</v>
       </c>
       <c r="T50">
-        <v>1.697369364300518</v>
+        <v>1.726609337910991</v>
       </c>
       <c r="U50">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V50">
         <v>0.21</v>
       </c>
       <c r="W50">
-        <v>0.056801</v>
+        <v>0.059882</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.511960679224477</v>
+        <v>2.334090435663001</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1049241263988557</v>
+        <v>0.1049426966079321</v>
       </c>
       <c r="C51">
-        <v>99.54218667248267</v>
+        <v>97.4814609080408</v>
       </c>
       <c r="D51">
-        <v>157.7711866724827</v>
+        <v>157.7314609080408</v>
       </c>
       <c r="E51">
-        <v>80.62899999999999</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="F51">
-        <v>99.029</v>
+        <v>101.05</v>
       </c>
       <c r="G51">
         <v>40.8</v>
@@ -5469,28 +5469,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M51">
-        <v>7.5063982</v>
+        <v>7.659590000000001</v>
       </c>
       <c r="N51">
-        <v>10.01421404489796</v>
+        <v>9.86102224489796</v>
       </c>
       <c r="O51">
-        <v>2.102984949428572</v>
+        <v>2.070814671428571</v>
       </c>
       <c r="P51">
-        <v>7.911229095469389</v>
+        <v>7.790207573469388</v>
       </c>
       <c r="Q51">
-        <v>11.92122909546939</v>
+        <v>11.80020757346939</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.148199894899717</v>
+        <v>0.1500033932158641</v>
       </c>
       <c r="T51">
-        <v>1.726609337910991</v>
+        <v>1.757018910465883</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.334090435663001</v>
+        <v>2.28740862694974</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1049426966079321</v>
+        <v>0.1049612668170084</v>
       </c>
       <c r="C52">
-        <v>97.4814609080408</v>
+        <v>95.42075514394415</v>
       </c>
       <c r="D52">
-        <v>157.7314609080408</v>
+        <v>157.6917551439441</v>
       </c>
       <c r="E52">
-        <v>82.65000000000001</v>
+        <v>84.67099999999999</v>
       </c>
       <c r="F52">
-        <v>101.05</v>
+        <v>103.071</v>
       </c>
       <c r="G52">
         <v>40.8</v>
@@ -5551,28 +5551,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M52">
-        <v>7.659590000000001</v>
+        <v>7.812781800000001</v>
       </c>
       <c r="N52">
-        <v>9.86102224489796</v>
+        <v>9.707830444897962</v>
       </c>
       <c r="O52">
-        <v>2.070814671428571</v>
+        <v>2.038644393428572</v>
       </c>
       <c r="P52">
-        <v>7.790207573469388</v>
+        <v>7.669186051469389</v>
       </c>
       <c r="Q52">
-        <v>11.80020757346939</v>
+        <v>11.67918605146939</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1500033932158641</v>
+        <v>0.1518805037081805</v>
       </c>
       <c r="T52">
-        <v>1.757018910465883</v>
+        <v>1.788669690063832</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.28740862694974</v>
+        <v>2.242557477401706</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1049612668170084</v>
+        <v>0.1049798370260848</v>
       </c>
       <c r="C53">
-        <v>95.42075514394415</v>
+        <v>93.36006936509237</v>
       </c>
       <c r="D53">
-        <v>157.6917551439441</v>
+        <v>157.6520693650924</v>
       </c>
       <c r="E53">
-        <v>84.67099999999999</v>
+        <v>86.69200000000001</v>
       </c>
       <c r="F53">
-        <v>103.071</v>
+        <v>105.092</v>
       </c>
       <c r="G53">
         <v>40.8</v>
@@ -5633,28 +5633,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M53">
-        <v>7.812781800000001</v>
+        <v>7.965973600000001</v>
       </c>
       <c r="N53">
-        <v>9.707830444897962</v>
+        <v>9.55463864489796</v>
       </c>
       <c r="O53">
-        <v>2.038644393428572</v>
+        <v>2.006474115428571</v>
       </c>
       <c r="P53">
-        <v>7.669186051469389</v>
+        <v>7.548164529469388</v>
       </c>
       <c r="Q53">
-        <v>11.67918605146939</v>
+        <v>11.55816452946939</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1518805037081805</v>
+        <v>0.1538358271376766</v>
       </c>
       <c r="T53">
-        <v>1.788669690063832</v>
+        <v>1.821639252145029</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.242557477401706</v>
+        <v>2.199431372067058</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1049798370260848</v>
+        <v>0.1049984072351612</v>
       </c>
       <c r="C54">
-        <v>93.36006936509237</v>
+        <v>91.29940355640042</v>
       </c>
       <c r="D54">
-        <v>157.6520693650924</v>
+        <v>157.6124035564004</v>
       </c>
       <c r="E54">
-        <v>86.69200000000001</v>
+        <v>88.71299999999999</v>
       </c>
       <c r="F54">
-        <v>105.092</v>
+        <v>107.113</v>
       </c>
       <c r="G54">
         <v>40.8</v>
@@ -5715,28 +5715,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M54">
-        <v>7.965973600000001</v>
+        <v>8.1191654</v>
       </c>
       <c r="N54">
-        <v>9.55463864489796</v>
+        <v>9.401446844897961</v>
       </c>
       <c r="O54">
-        <v>2.006474115428571</v>
+        <v>1.974303837428572</v>
       </c>
       <c r="P54">
-        <v>7.548164529469388</v>
+        <v>7.42714300746939</v>
       </c>
       <c r="Q54">
-        <v>11.55816452946939</v>
+        <v>11.43714300746939</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1538358271376766</v>
+        <v>0.1558743558194918</v>
       </c>
       <c r="T54">
-        <v>1.821639252145029</v>
+        <v>1.856011774314787</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.199431372067058</v>
+        <v>2.157932666933717</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1049984072351612</v>
+        <v>0.1050169774442375</v>
       </c>
       <c r="C55">
-        <v>91.29940355640042</v>
+        <v>89.23875770279842</v>
       </c>
       <c r="D55">
-        <v>157.6124035564004</v>
+        <v>157.5727577027984</v>
       </c>
       <c r="E55">
-        <v>88.71299999999999</v>
+        <v>90.73400000000001</v>
       </c>
       <c r="F55">
-        <v>107.113</v>
+        <v>109.134</v>
       </c>
       <c r="G55">
         <v>40.8</v>
@@ -5797,28 +5797,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M55">
-        <v>8.1191654</v>
+        <v>8.2723572</v>
       </c>
       <c r="N55">
-        <v>9.401446844897961</v>
+        <v>9.248255044897961</v>
       </c>
       <c r="O55">
-        <v>1.974303837428572</v>
+        <v>1.942133559428572</v>
       </c>
       <c r="P55">
-        <v>7.42714300746939</v>
+        <v>7.306121485469389</v>
       </c>
       <c r="Q55">
-        <v>11.43714300746939</v>
+        <v>11.31612148546939</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1558743558194918</v>
+        <v>0.158001516183125</v>
       </c>
       <c r="T55">
-        <v>1.856011774314787</v>
+        <v>1.891878753970187</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.157932666933717</v>
+        <v>2.117970950879389</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1050169774442375</v>
+        <v>0.1050355476533139</v>
       </c>
       <c r="C56">
-        <v>89.23875770279842</v>
+        <v>87.17813178923163</v>
       </c>
       <c r="D56">
-        <v>157.5727577027984</v>
+        <v>157.5331317892316</v>
       </c>
       <c r="E56">
-        <v>90.73400000000001</v>
+        <v>92.755</v>
       </c>
       <c r="F56">
-        <v>109.134</v>
+        <v>111.155</v>
       </c>
       <c r="G56">
         <v>40.8</v>
@@ -5879,28 +5879,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M56">
-        <v>8.2723572</v>
+        <v>8.425549</v>
       </c>
       <c r="N56">
-        <v>9.248255044897961</v>
+        <v>9.095063244897961</v>
       </c>
       <c r="O56">
-        <v>1.942133559428572</v>
+        <v>1.909963281428572</v>
       </c>
       <c r="P56">
-        <v>7.306121485469389</v>
+        <v>7.185099963469389</v>
       </c>
       <c r="Q56">
-        <v>11.31612148546939</v>
+        <v>11.19509996346939</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.158001516183125</v>
+        <v>0.1602232170073642</v>
       </c>
       <c r="T56">
-        <v>1.891878753970187</v>
+        <v>1.929339821610272</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.117970950879389</v>
+        <v>2.079462388136128</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1050355476533139</v>
+        <v>0.1050541178623902</v>
       </c>
       <c r="C57">
-        <v>87.17813178923163</v>
+        <v>85.11752580066052</v>
       </c>
       <c r="D57">
-        <v>157.5331317892316</v>
+        <v>157.4935258006605</v>
       </c>
       <c r="E57">
-        <v>92.755</v>
+        <v>94.77600000000001</v>
       </c>
       <c r="F57">
-        <v>111.155</v>
+        <v>113.176</v>
       </c>
       <c r="G57">
         <v>40.8</v>
@@ -5961,28 +5961,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M57">
-        <v>8.425549</v>
+        <v>8.5787408</v>
       </c>
       <c r="N57">
-        <v>9.095063244897961</v>
+        <v>8.941871444897961</v>
       </c>
       <c r="O57">
-        <v>1.909963281428572</v>
+        <v>1.877793003428572</v>
       </c>
       <c r="P57">
-        <v>7.185099963469389</v>
+        <v>7.064078441469389</v>
       </c>
       <c r="Q57">
-        <v>11.19509996346939</v>
+        <v>11.07407844146939</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1602232170073642</v>
+        <v>0.1625459042327051</v>
       </c>
       <c r="T57">
-        <v>1.929339821610272</v>
+        <v>1.968503665052178</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.079462388136128</v>
+        <v>2.042329131205125</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1050541178623902</v>
+        <v>0.1050726880714666</v>
       </c>
       <c r="C58">
-        <v>85.11752580066052</v>
+        <v>83.05693972206046</v>
       </c>
       <c r="D58">
-        <v>157.4935258006605</v>
+        <v>157.4539397220605</v>
       </c>
       <c r="E58">
-        <v>94.77600000000001</v>
+        <v>96.797</v>
       </c>
       <c r="F58">
-        <v>113.176</v>
+        <v>115.197</v>
       </c>
       <c r="G58">
         <v>40.8</v>
@@ -6043,28 +6043,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M58">
-        <v>8.5787408</v>
+        <v>8.7319326</v>
       </c>
       <c r="N58">
-        <v>8.941871444897961</v>
+        <v>8.788679644897961</v>
       </c>
       <c r="O58">
-        <v>1.877793003428572</v>
+        <v>1.845622725428572</v>
       </c>
       <c r="P58">
-        <v>7.064078441469389</v>
+        <v>6.943056919469389</v>
       </c>
       <c r="Q58">
-        <v>11.07407844146939</v>
+        <v>10.95305691946939</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1625459042327051</v>
+        <v>0.1649766234220153</v>
       </c>
       <c r="T58">
-        <v>1.968503665052178</v>
+        <v>2.009489082607661</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.042329131205125</v>
+        <v>2.006498795569947</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1050726880714666</v>
+        <v>0.1115976982805429</v>
       </c>
       <c r="C59">
-        <v>83.05693972206046</v>
+        <v>68.25854508860073</v>
       </c>
       <c r="D59">
-        <v>157.4539397220605</v>
+        <v>144.6765450886008</v>
       </c>
       <c r="E59">
-        <v>96.797</v>
+        <v>98.81800000000001</v>
       </c>
       <c r="F59">
-        <v>115.197</v>
+        <v>117.218</v>
       </c>
       <c r="G59">
         <v>40.8</v>
@@ -6125,45 +6125,45 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M59">
-        <v>8.7319326</v>
+        <v>10.54962</v>
       </c>
       <c r="N59">
-        <v>8.788679644897961</v>
+        <v>6.97099224489796</v>
       </c>
       <c r="O59">
-        <v>1.845622725428572</v>
+        <v>1.463908371428572</v>
       </c>
       <c r="P59">
-        <v>6.943056919469389</v>
+        <v>5.507083873469389</v>
       </c>
       <c r="Q59">
-        <v>10.95305691946939</v>
+        <v>9.517083873469389</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1649766234220153</v>
+        <v>0.1675230911441499</v>
       </c>
       <c r="T59">
-        <v>2.009489082607661</v>
+        <v>2.052426186713406</v>
       </c>
       <c r="U59">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V59">
         <v>0.21</v>
       </c>
       <c r="W59">
-        <v>0.059882</v>
+        <v>0.0711</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.006498795569947</v>
+        <v>1.6607813594137</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1115976982805429</v>
+        <v>0.1117284484896193</v>
       </c>
       <c r="C60">
-        <v>68.25854508860075</v>
+        <v>66.00266702107926</v>
       </c>
       <c r="D60">
-        <v>144.6765450886008</v>
+        <v>144.4416670210793</v>
       </c>
       <c r="E60">
-        <v>98.81799999999998</v>
+        <v>100.839</v>
       </c>
       <c r="F60">
-        <v>117.218</v>
+        <v>119.239</v>
       </c>
       <c r="G60">
         <v>40.8</v>
@@ -6207,28 +6207,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M60">
-        <v>10.54962</v>
+        <v>10.73151</v>
       </c>
       <c r="N60">
-        <v>6.970992244897962</v>
+        <v>6.789102244897963</v>
       </c>
       <c r="O60">
-        <v>1.463908371428572</v>
+        <v>1.425711471428572</v>
       </c>
       <c r="P60">
-        <v>5.50708387346939</v>
+        <v>5.363390773469391</v>
       </c>
       <c r="Q60">
-        <v>9.517083873469389</v>
+        <v>9.37339077346939</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1675230911441499</v>
+        <v>0.1701937768039495</v>
       </c>
       <c r="T60">
-        <v>2.052426186713406</v>
+        <v>2.097457783702357</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.6607813594137</v>
+        <v>1.632632522813468</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1117284484896193</v>
+        <v>0.1118591986986956</v>
       </c>
       <c r="C61">
-        <v>66.00266702107926</v>
+        <v>63.7475503525614</v>
       </c>
       <c r="D61">
-        <v>144.4416670210793</v>
+        <v>144.2075503525614</v>
       </c>
       <c r="E61">
-        <v>100.839</v>
+        <v>102.86</v>
       </c>
       <c r="F61">
-        <v>119.239</v>
+        <v>121.26</v>
       </c>
       <c r="G61">
         <v>40.8</v>
@@ -6289,28 +6289,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M61">
-        <v>10.73151</v>
+        <v>10.9134</v>
       </c>
       <c r="N61">
-        <v>6.789102244897963</v>
+        <v>6.607212244897962</v>
       </c>
       <c r="O61">
-        <v>1.425711471428572</v>
+        <v>1.387514571428572</v>
       </c>
       <c r="P61">
-        <v>5.363390773469391</v>
+        <v>5.219697673469391</v>
       </c>
       <c r="Q61">
-        <v>9.37339077346939</v>
+        <v>9.22969767346939</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1701937768039495</v>
+        <v>0.1729979967467391</v>
       </c>
       <c r="T61">
-        <v>2.097457783702357</v>
+        <v>2.144740960540756</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.632632522813468</v>
+        <v>1.605421980766577</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1118591986986956</v>
+        <v>0.111989948907772</v>
       </c>
       <c r="C62">
-        <v>63.7475503525614</v>
+        <v>61.49319138672298</v>
       </c>
       <c r="D62">
-        <v>144.2075503525614</v>
+        <v>143.974191386723</v>
       </c>
       <c r="E62">
-        <v>102.86</v>
+        <v>104.881</v>
       </c>
       <c r="F62">
-        <v>121.26</v>
+        <v>123.281</v>
       </c>
       <c r="G62">
         <v>40.8</v>
@@ -6371,28 +6371,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M62">
-        <v>10.9134</v>
+        <v>11.09529</v>
       </c>
       <c r="N62">
-        <v>6.607212244897962</v>
+        <v>6.425322244897963</v>
       </c>
       <c r="O62">
-        <v>1.387514571428572</v>
+        <v>1.349317671428572</v>
       </c>
       <c r="P62">
-        <v>5.219697673469391</v>
+        <v>5.07600457346939</v>
       </c>
       <c r="Q62">
-        <v>9.22969767346939</v>
+        <v>9.08600457346939</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1729979967467391</v>
+        <v>0.1759460228404411</v>
       </c>
       <c r="T62">
-        <v>2.144740960540756</v>
+        <v>2.19444891567856</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.605421980766577</v>
+        <v>1.579103587639256</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.111989948907772</v>
+        <v>0.1121206991168484</v>
       </c>
       <c r="C63">
-        <v>61.49319138672298</v>
+        <v>59.23958645112705</v>
       </c>
       <c r="D63">
-        <v>143.974191386723</v>
+        <v>143.741586451127</v>
       </c>
       <c r="E63">
-        <v>104.881</v>
+        <v>106.902</v>
       </c>
       <c r="F63">
-        <v>123.281</v>
+        <v>125.302</v>
       </c>
       <c r="G63">
         <v>40.8</v>
@@ -6453,28 +6453,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M63">
-        <v>11.09529</v>
+        <v>11.27718</v>
       </c>
       <c r="N63">
-        <v>6.425322244897963</v>
+        <v>6.243432244897962</v>
       </c>
       <c r="O63">
-        <v>1.349317671428572</v>
+        <v>1.311120771428572</v>
       </c>
       <c r="P63">
-        <v>5.07600457346939</v>
+        <v>4.93231147346939</v>
       </c>
       <c r="Q63">
-        <v>9.08600457346939</v>
+        <v>8.94231147346939</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1759460228404411</v>
+        <v>0.1790492082022326</v>
       </c>
       <c r="T63">
-        <v>2.19444891567856</v>
+        <v>2.246773078981513</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.579103587639256</v>
+        <v>1.553634174935397</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1121206991168484</v>
+        <v>0.1122514493259247</v>
       </c>
       <c r="C64">
-        <v>59.23958645112705</v>
+        <v>56.98673189703099</v>
       </c>
       <c r="D64">
-        <v>143.741586451127</v>
+        <v>143.509731897031</v>
       </c>
       <c r="E64">
-        <v>106.902</v>
+        <v>108.923</v>
       </c>
       <c r="F64">
-        <v>125.302</v>
+        <v>127.323</v>
       </c>
       <c r="G64">
         <v>40.8</v>
@@ -6535,28 +6535,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M64">
-        <v>11.27718</v>
+        <v>11.45907</v>
       </c>
       <c r="N64">
-        <v>6.243432244897962</v>
+        <v>6.061542244897963</v>
       </c>
       <c r="O64">
-        <v>1.311120771428572</v>
+        <v>1.272923871428572</v>
       </c>
       <c r="P64">
-        <v>4.93231147346939</v>
+        <v>4.78861837346939</v>
       </c>
       <c r="Q64">
-        <v>8.94231147346939</v>
+        <v>8.79861837346939</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1790492082022326</v>
+        <v>0.1823201333133102</v>
       </c>
       <c r="T64">
-        <v>2.246773078981513</v>
+        <v>2.301925575435976</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.553634174935397</v>
+        <v>1.528973315015788</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1122514493259247</v>
+        <v>0.1123821995350011</v>
       </c>
       <c r="C65">
-        <v>56.98673189703099</v>
+        <v>54.73462409919614</v>
       </c>
       <c r="D65">
-        <v>143.509731897031</v>
+        <v>143.2786240991962</v>
       </c>
       <c r="E65">
-        <v>108.923</v>
+        <v>110.944</v>
       </c>
       <c r="F65">
-        <v>127.323</v>
+        <v>129.344</v>
       </c>
       <c r="G65">
         <v>40.8</v>
@@ -6617,28 +6617,28 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M65">
-        <v>11.45907</v>
+        <v>11.64096</v>
       </c>
       <c r="N65">
-        <v>6.061542244897963</v>
+        <v>5.879652244897962</v>
       </c>
       <c r="O65">
-        <v>1.272923871428572</v>
+        <v>1.234726971428572</v>
       </c>
       <c r="P65">
-        <v>4.78861837346939</v>
+        <v>4.64492527346939</v>
       </c>
       <c r="Q65">
-        <v>8.79861837346939</v>
+        <v>8.65492527346939</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1823201333133102</v>
+        <v>0.1857727764861142</v>
       </c>
       <c r="T65">
-        <v>2.301925575435976</v>
+        <v>2.360142099471242</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.528973315015788</v>
+        <v>1.505083106968666</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1123821995350011</v>
+        <v>0.1442392355784485</v>
       </c>
       <c r="C66">
-        <v>54.73462409919614</v>
+        <v>12.33766555479434</v>
       </c>
       <c r="D66">
-        <v>143.2786240991962</v>
+        <v>102.9026655547943</v>
       </c>
       <c r="E66">
-        <v>110.944</v>
+        <v>112.965</v>
       </c>
       <c r="F66">
-        <v>129.344</v>
+        <v>131.365</v>
       </c>
       <c r="G66">
         <v>40.8</v>
@@ -6699,45 +6699,45 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M66">
-        <v>11.64096</v>
+        <v>19.284382</v>
       </c>
       <c r="N66">
-        <v>5.879652244897962</v>
+        <v>-1.763769755102043</v>
       </c>
       <c r="O66">
-        <v>1.234726971428572</v>
+        <v>-0.370391648571429</v>
       </c>
       <c r="P66">
-        <v>4.64492527346939</v>
+        <v>-1.393378106530614</v>
       </c>
       <c r="Q66">
-        <v>8.65492527346939</v>
+        <v>2.616621893469386</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1857727764861142</v>
+        <v>0.1914992024009756</v>
       </c>
       <c r="T66">
-        <v>2.360142099471242</v>
+        <v>2.456697867103015</v>
       </c>
       <c r="U66">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.21</v>
+        <v>0.19079318027555</v>
       </c>
       <c r="W66">
-        <v>0.0711</v>
+        <v>0.1187915611355493</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>1.505083106968666</v>
+        <v>0.9085389536930951</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1442392355784485</v>
+        <v>0.1452492355784484</v>
       </c>
       <c r="C67">
-        <v>12.33766555479434</v>
+        <v>9.405449809083535</v>
       </c>
       <c r="D67">
-        <v>102.9026655547943</v>
+        <v>101.9914498090835</v>
       </c>
       <c r="E67">
-        <v>112.965</v>
+        <v>114.986</v>
       </c>
       <c r="F67">
-        <v>131.365</v>
+        <v>133.386</v>
       </c>
       <c r="G67">
         <v>40.8</v>
@@ -6781,37 +6781,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M67">
-        <v>19.284382</v>
+        <v>19.5810648</v>
       </c>
       <c r="N67">
-        <v>-1.763769755102043</v>
+        <v>-2.060452555102039</v>
       </c>
       <c r="O67">
-        <v>-0.370391648571429</v>
+        <v>-0.4326950365714281</v>
       </c>
       <c r="P67">
-        <v>-1.393378106530614</v>
+        <v>-1.627757518530611</v>
       </c>
       <c r="Q67">
-        <v>2.616621893469386</v>
+        <v>2.382242481469389</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1914992024009756</v>
+        <v>0.1957844730598277</v>
       </c>
       <c r="T67">
-        <v>2.456697867103015</v>
+        <v>2.528953686723692</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.19079318027555</v>
+        <v>0.1879023745137993</v>
       </c>
       <c r="W67">
-        <v>0.1187915611355493</v>
+        <v>0.1192159314213743</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.9085389536930951</v>
+        <v>0.8947732119704727</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1452492355784484</v>
+        <v>0.1462592355784485</v>
       </c>
       <c r="C68">
-        <v>9.405449809083535</v>
+        <v>6.489230269753307</v>
       </c>
       <c r="D68">
-        <v>101.9914498090835</v>
+        <v>101.0962302697533</v>
       </c>
       <c r="E68">
-        <v>114.986</v>
+        <v>117.007</v>
       </c>
       <c r="F68">
-        <v>133.386</v>
+        <v>135.407</v>
       </c>
       <c r="G68">
         <v>40.8</v>
@@ -6863,37 +6863,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M68">
-        <v>19.5810648</v>
+        <v>19.8777476</v>
       </c>
       <c r="N68">
-        <v>-2.060452555102039</v>
+        <v>-2.357135355102042</v>
       </c>
       <c r="O68">
-        <v>-0.4326950365714281</v>
+        <v>-0.4949984245714287</v>
       </c>
       <c r="P68">
-        <v>-1.627757518530611</v>
+        <v>-1.862136930530613</v>
       </c>
       <c r="Q68">
-        <v>2.382242481469389</v>
+        <v>2.147863069469387</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1957844730598277</v>
+        <v>0.2003294570919438</v>
       </c>
       <c r="T68">
-        <v>2.528953686723692</v>
+        <v>2.605588646927441</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.1879023745137993</v>
+        <v>0.1850978614613545</v>
       </c>
       <c r="W68">
-        <v>0.1192159314213743</v>
+        <v>0.1196276339374732</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8947732119704727</v>
+        <v>0.8814183879112117</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1462592355784485</v>
+        <v>0.1472692355784485</v>
       </c>
       <c r="C69">
-        <v>6.489230269753307</v>
+        <v>3.588589386602365</v>
       </c>
       <c r="D69">
-        <v>101.0962302697533</v>
+        <v>100.2165893866024</v>
       </c>
       <c r="E69">
-        <v>117.007</v>
+        <v>119.028</v>
       </c>
       <c r="F69">
-        <v>135.407</v>
+        <v>137.428</v>
       </c>
       <c r="G69">
         <v>40.8</v>
@@ -6945,37 +6945,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M69">
-        <v>19.8777476</v>
+        <v>20.1744304</v>
       </c>
       <c r="N69">
-        <v>-2.357135355102042</v>
+        <v>-2.653818155102041</v>
       </c>
       <c r="O69">
-        <v>-0.4949984245714287</v>
+        <v>-0.5573018125714285</v>
       </c>
       <c r="P69">
-        <v>-1.862136930530613</v>
+        <v>-2.096516342530612</v>
       </c>
       <c r="Q69">
-        <v>2.147863069469387</v>
+        <v>1.913483657469388</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2003294570919438</v>
+        <v>0.205158502626067</v>
       </c>
       <c r="T69">
-        <v>2.605588646927441</v>
+        <v>2.687013292143923</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.1850978614613545</v>
+        <v>0.1823758340869228</v>
       </c>
       <c r="W69">
-        <v>0.1196276339374732</v>
+        <v>0.1200272275560397</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8814183879112117</v>
+        <v>0.8684563527948704</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1472692355784485</v>
+        <v>0.1482792355784485</v>
       </c>
       <c r="C70">
-        <v>3.588589386602365</v>
+        <v>0.7031240165322572</v>
       </c>
       <c r="D70">
-        <v>100.2165893866024</v>
+        <v>99.35212401653227</v>
       </c>
       <c r="E70">
-        <v>119.028</v>
+        <v>121.049</v>
       </c>
       <c r="F70">
-        <v>137.428</v>
+        <v>139.449</v>
       </c>
       <c r="G70">
         <v>40.8</v>
@@ -7027,37 +7027,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M70">
-        <v>20.1744304</v>
+        <v>20.4711132</v>
       </c>
       <c r="N70">
-        <v>-2.653818155102041</v>
+        <v>-2.950500955102044</v>
       </c>
       <c r="O70">
-        <v>-0.5573018125714285</v>
+        <v>-0.6196052005714291</v>
       </c>
       <c r="P70">
-        <v>-2.096516342530612</v>
+        <v>-2.330895754530614</v>
       </c>
       <c r="Q70">
-        <v>1.913483657469388</v>
+        <v>1.679104245469385</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.205158502626067</v>
+        <v>0.2102990994849724</v>
       </c>
       <c r="T70">
-        <v>2.687013292143923</v>
+        <v>2.773691140277598</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.1823758340869228</v>
+        <v>0.1797327060566775</v>
       </c>
       <c r="W70">
-        <v>0.1200272275560397</v>
+        <v>0.1204152387508798</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8684563527948704</v>
+        <v>0.8558700288413215</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1482792355784485</v>
+        <v>0.1492892355784485</v>
       </c>
       <c r="C71">
-        <v>0.7031240165322572</v>
+        <v>-2.167555192513845</v>
       </c>
       <c r="D71">
-        <v>99.35212401653227</v>
+        <v>98.50244480748614</v>
       </c>
       <c r="E71">
-        <v>121.049</v>
+        <v>123.07</v>
       </c>
       <c r="F71">
-        <v>139.449</v>
+        <v>141.47</v>
       </c>
       <c r="G71">
         <v>40.8</v>
@@ -7109,37 +7109,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M71">
-        <v>20.4711132</v>
+        <v>20.767796</v>
       </c>
       <c r="N71">
-        <v>-2.950500955102044</v>
+        <v>-3.247183755102039</v>
       </c>
       <c r="O71">
-        <v>-0.6196052005714291</v>
+        <v>-0.6819085885714282</v>
       </c>
       <c r="P71">
-        <v>-2.330895754530614</v>
+        <v>-2.565275166530611</v>
       </c>
       <c r="Q71">
-        <v>1.679104245469385</v>
+        <v>1.444724833469389</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2102990994849724</v>
+        <v>0.2157824028011382</v>
       </c>
       <c r="T71">
-        <v>2.773691140277598</v>
+        <v>2.866147511620185</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.1797327060566775</v>
+        <v>0.1771650959701536</v>
       </c>
       <c r="W71">
-        <v>0.1204152387508798</v>
+        <v>0.1207921639115815</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8558700288413215</v>
+        <v>0.8436433141435885</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1492892355784485</v>
+        <v>0.1502992355784485</v>
       </c>
       <c r="C72">
-        <v>-2.167555192513845</v>
+        <v>-5.023824386269979</v>
       </c>
       <c r="D72">
-        <v>98.50244480748614</v>
+        <v>97.66717561373004</v>
       </c>
       <c r="E72">
-        <v>123.07</v>
+        <v>125.091</v>
       </c>
       <c r="F72">
-        <v>141.47</v>
+        <v>143.491</v>
       </c>
       <c r="G72">
         <v>40.8</v>
@@ -7191,37 +7191,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M72">
-        <v>20.767796</v>
+        <v>21.0644788</v>
       </c>
       <c r="N72">
-        <v>-3.247183755102039</v>
+        <v>-3.543866555102042</v>
       </c>
       <c r="O72">
-        <v>-0.6819085885714282</v>
+        <v>-0.7442119765714288</v>
       </c>
       <c r="P72">
-        <v>-2.565275166530611</v>
+        <v>-2.799654578530613</v>
       </c>
       <c r="Q72">
-        <v>1.444724833469389</v>
+        <v>1.210345421469387</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2157824028011382</v>
+        <v>0.2216438649666947</v>
       </c>
       <c r="T72">
-        <v>2.866147511620185</v>
+        <v>2.964980184434674</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.1771650959701536</v>
+        <v>0.1746698129283204</v>
       </c>
       <c r="W72">
-        <v>0.1207921639115815</v>
+        <v>0.1211584714621226</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8436433141435885</v>
+        <v>0.831761013944383</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1502992355784485</v>
+        <v>0.1513092355784485</v>
       </c>
       <c r="C73">
-        <v>-5.023824386269951</v>
+        <v>-7.866047059365599</v>
       </c>
       <c r="D73">
-        <v>97.66717561373004</v>
+        <v>96.84595294063439</v>
       </c>
       <c r="E73">
-        <v>125.091</v>
+        <v>127.112</v>
       </c>
       <c r="F73">
-        <v>143.491</v>
+        <v>145.512</v>
       </c>
       <c r="G73">
         <v>40.8</v>
@@ -7273,37 +7273,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M73">
-        <v>21.0644788</v>
+        <v>21.3611616</v>
       </c>
       <c r="N73">
-        <v>-3.543866555102039</v>
+        <v>-3.840549355102041</v>
       </c>
       <c r="O73">
-        <v>-0.744211976571428</v>
+        <v>-0.8065153645714287</v>
       </c>
       <c r="P73">
-        <v>-2.79965457853061</v>
+        <v>-3.034033990530613</v>
       </c>
       <c r="Q73">
-        <v>1.210345421469389</v>
+        <v>0.9759660094693872</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2216438649666946</v>
+        <v>0.2279240030012194</v>
       </c>
       <c r="T73">
-        <v>2.964980184434673</v>
+        <v>3.070872333878769</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.1746698129283204</v>
+        <v>0.172243843304316</v>
       </c>
       <c r="W73">
-        <v>0.1211584714621226</v>
+        <v>0.1215146038029264</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8317610139443831</v>
+        <v>0.8202087776395999</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1513092355784485</v>
+        <v>0.1523192355784485</v>
       </c>
       <c r="C74">
-        <v>-7.866047059365599</v>
+        <v>-10.69457458276779</v>
       </c>
       <c r="D74">
-        <v>96.84595294063439</v>
+        <v>96.03842541723222</v>
       </c>
       <c r="E74">
-        <v>127.112</v>
+        <v>129.133</v>
       </c>
       <c r="F74">
-        <v>145.512</v>
+        <v>147.533</v>
       </c>
       <c r="G74">
         <v>40.8</v>
@@ -7355,37 +7355,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M74">
-        <v>21.3611616</v>
+        <v>21.6578444</v>
       </c>
       <c r="N74">
-        <v>-3.840549355102041</v>
+        <v>-4.137232155102041</v>
       </c>
       <c r="O74">
-        <v>-0.8065153645714287</v>
+        <v>-0.8688187525714285</v>
       </c>
       <c r="P74">
-        <v>-3.034033990530613</v>
+        <v>-3.268413402530612</v>
       </c>
       <c r="Q74">
-        <v>0.9759660094693872</v>
+        <v>0.7415865974693876</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2279240030012194</v>
+        <v>0.234669336445709</v>
       </c>
       <c r="T74">
-        <v>3.070872333878769</v>
+        <v>3.184608346244649</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.172243843304316</v>
+        <v>0.1698843386015171</v>
       </c>
       <c r="W74">
-        <v>0.1215146038029264</v>
+        <v>0.1218609790932973</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8202087776395999</v>
+        <v>0.8089730409596054</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1523192355784485</v>
+        <v>0.195230725254463</v>
       </c>
       <c r="C75">
-        <v>-10.69457458276779</v>
+        <v>-37.83845875911358</v>
       </c>
       <c r="D75">
-        <v>96.03842541723222</v>
+        <v>70.91554124088643</v>
       </c>
       <c r="E75">
-        <v>129.133</v>
+        <v>131.154</v>
       </c>
       <c r="F75">
-        <v>147.533</v>
+        <v>149.554</v>
       </c>
       <c r="G75">
         <v>40.8</v>
@@ -7437,45 +7437,45 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M75">
-        <v>21.6578444</v>
+        <v>30.0304432</v>
       </c>
       <c r="N75">
-        <v>-4.137232155102041</v>
+        <v>-12.50983095510204</v>
       </c>
       <c r="O75">
-        <v>-0.8688187525714285</v>
+        <v>-2.627064500571428</v>
       </c>
       <c r="P75">
-        <v>-3.268413402530612</v>
+        <v>-9.882766454530611</v>
       </c>
       <c r="Q75">
-        <v>0.7415865974693876</v>
+        <v>-5.872766454530611</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.234669336445709</v>
+        <v>0.2494008096782922</v>
       </c>
       <c r="T75">
-        <v>3.184608346244649</v>
+        <v>3.433002148498779</v>
       </c>
       <c r="U75">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1698843386015171</v>
+        <v>0.1225199557304093</v>
       </c>
       <c r="W75">
-        <v>0.1218609790932973</v>
+        <v>0.1761979928893338</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.8089730409596054</v>
+        <v>0.5834283606209968</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.195230725254463</v>
+        <v>0.196780725254463</v>
       </c>
       <c r="C76">
-        <v>-37.83845875911358</v>
+        <v>-40.52326241858646</v>
       </c>
       <c r="D76">
-        <v>70.91554124088643</v>
+        <v>70.25173758141354</v>
       </c>
       <c r="E76">
-        <v>131.154</v>
+        <v>133.175</v>
       </c>
       <c r="F76">
-        <v>149.554</v>
+        <v>151.575</v>
       </c>
       <c r="G76">
         <v>40.8</v>
@@ -7519,37 +7519,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M76">
-        <v>30.0304432</v>
+        <v>30.43626</v>
       </c>
       <c r="N76">
-        <v>-12.50983095510204</v>
+        <v>-12.91564775510204</v>
       </c>
       <c r="O76">
-        <v>-2.627064500571428</v>
+        <v>-2.712286028571428</v>
       </c>
       <c r="P76">
-        <v>-9.882766454530611</v>
+        <v>-10.20336172653061</v>
       </c>
       <c r="Q76">
-        <v>-5.872766454530611</v>
+        <v>-6.193361726530609</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2494008096782922</v>
+        <v>0.2575448420654239</v>
       </c>
       <c r="T76">
-        <v>3.433002148498779</v>
+        <v>3.570322234438729</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1225199557304093</v>
+        <v>0.1208863563206706</v>
       </c>
       <c r="W76">
-        <v>0.1761979928893338</v>
+        <v>0.1765260196508094</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5834283606209968</v>
+        <v>0.5756493158127169</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.196780725254463</v>
+        <v>0.198330725254463</v>
       </c>
       <c r="C77">
-        <v>-40.52326241858646</v>
+        <v>-43.19575427780629</v>
       </c>
       <c r="D77">
-        <v>70.25173758141354</v>
+        <v>69.60024572219372</v>
       </c>
       <c r="E77">
-        <v>133.175</v>
+        <v>135.196</v>
       </c>
       <c r="F77">
-        <v>151.575</v>
+        <v>153.596</v>
       </c>
       <c r="G77">
         <v>40.8</v>
@@ -7601,37 +7601,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M77">
-        <v>30.43626</v>
+        <v>30.8420768</v>
       </c>
       <c r="N77">
-        <v>-12.91564775510204</v>
+        <v>-13.32146455510204</v>
       </c>
       <c r="O77">
-        <v>-2.712286028571428</v>
+        <v>-2.797507556571428</v>
       </c>
       <c r="P77">
-        <v>-10.20336172653061</v>
+        <v>-10.52395699853061</v>
       </c>
       <c r="Q77">
-        <v>-6.193361726530609</v>
+        <v>-6.513956998530611</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2575448420654239</v>
+        <v>0.2663675438181499</v>
       </c>
       <c r="T77">
-        <v>3.570322234438729</v>
+        <v>3.719085660873677</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1208863563206706</v>
+        <v>0.1192957463690828</v>
       </c>
       <c r="W77">
-        <v>0.1765260196508094</v>
+        <v>0.1768454141290882</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5756493158127169</v>
+        <v>0.5680749827099179</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.198330725254463</v>
+        <v>0.199880725254463</v>
       </c>
       <c r="C78">
-        <v>-43.19575427780629</v>
+        <v>-45.85627371641907</v>
       </c>
       <c r="D78">
-        <v>69.60024572219372</v>
+        <v>68.96072628358093</v>
       </c>
       <c r="E78">
-        <v>135.196</v>
+        <v>137.217</v>
       </c>
       <c r="F78">
-        <v>153.596</v>
+        <v>155.617</v>
       </c>
       <c r="G78">
         <v>40.8</v>
@@ -7683,37 +7683,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M78">
-        <v>30.8420768</v>
+        <v>31.2478936</v>
       </c>
       <c r="N78">
-        <v>-13.32146455510204</v>
+        <v>-13.72728135510204</v>
       </c>
       <c r="O78">
-        <v>-2.797507556571428</v>
+        <v>-2.882729084571428</v>
       </c>
       <c r="P78">
-        <v>-10.52395699853061</v>
+        <v>-10.84455227053061</v>
       </c>
       <c r="Q78">
-        <v>-6.513956998530611</v>
+        <v>-6.83455227053061</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2663675438181499</v>
+        <v>0.2759574370276347</v>
       </c>
       <c r="T78">
-        <v>3.719085660873677</v>
+        <v>3.880785037433402</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1192957463690828</v>
+        <v>0.1177464509616921</v>
       </c>
       <c r="W78">
-        <v>0.1768454141290882</v>
+        <v>0.1771565126468922</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5680749827099179</v>
+        <v>0.5606973855318671</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.199880725254463</v>
+        <v>0.201430725254463</v>
       </c>
       <c r="C79">
-        <v>-45.85627371641907</v>
+        <v>-48.50514775412749</v>
       </c>
       <c r="D79">
-        <v>68.96072628358093</v>
+        <v>68.33285224587252</v>
       </c>
       <c r="E79">
-        <v>137.217</v>
+        <v>139.238</v>
       </c>
       <c r="F79">
-        <v>155.617</v>
+        <v>157.638</v>
       </c>
       <c r="G79">
         <v>40.8</v>
@@ -7765,37 +7765,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M79">
-        <v>31.2478936</v>
+        <v>31.6537104</v>
       </c>
       <c r="N79">
-        <v>-13.72728135510204</v>
+        <v>-14.13309815510204</v>
       </c>
       <c r="O79">
-        <v>-2.882729084571428</v>
+        <v>-2.967950612571428</v>
       </c>
       <c r="P79">
-        <v>-10.84455227053061</v>
+        <v>-11.16514754253061</v>
       </c>
       <c r="Q79">
-        <v>-6.83455227053061</v>
+        <v>-7.155147542530612</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2759574370276347</v>
+        <v>0.286419138710709</v>
       </c>
       <c r="T79">
-        <v>3.880785037433402</v>
+        <v>4.057184357316739</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1177464509616921</v>
+        <v>0.1162368810775678</v>
       </c>
       <c r="W79">
-        <v>0.1771565126468922</v>
+        <v>0.1774596342796244</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5606973855318671</v>
+        <v>0.5535089575122277</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.201430725254463</v>
+        <v>0.202980725254463</v>
       </c>
       <c r="C80">
-        <v>-48.50514775412749</v>
+        <v>-51.14269160828836</v>
       </c>
       <c r="D80">
-        <v>68.33285224587252</v>
+        <v>67.71630839171164</v>
       </c>
       <c r="E80">
-        <v>139.238</v>
+        <v>141.259</v>
       </c>
       <c r="F80">
-        <v>157.638</v>
+        <v>159.659</v>
       </c>
       <c r="G80">
         <v>40.8</v>
@@ -7847,37 +7847,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M80">
-        <v>31.6537104</v>
+        <v>32.0595272</v>
       </c>
       <c r="N80">
-        <v>-14.13309815510204</v>
+        <v>-14.53891495510204</v>
       </c>
       <c r="O80">
-        <v>-2.967950612571428</v>
+        <v>-3.053172140571427</v>
       </c>
       <c r="P80">
-        <v>-11.16514754253061</v>
+        <v>-11.48574281453061</v>
       </c>
       <c r="Q80">
-        <v>-7.155147542530612</v>
+        <v>-7.47574281453061</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.286419138710709</v>
+        <v>0.2978771929350285</v>
       </c>
       <c r="T80">
-        <v>4.057184357316739</v>
+        <v>4.25038361242706</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1162368810775678</v>
+        <v>0.1147655281525353</v>
       </c>
       <c r="W80">
-        <v>0.1774596342796244</v>
+        <v>0.1777550819469709</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5535089575122277</v>
+        <v>0.546502515012073</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.202980725254463</v>
+        <v>0.204530725254463</v>
       </c>
       <c r="C81">
-        <v>-51.14269160828836</v>
+        <v>-53.76920922159427</v>
       </c>
       <c r="D81">
-        <v>67.71630839171164</v>
+        <v>67.11079077840574</v>
       </c>
       <c r="E81">
-        <v>141.259</v>
+        <v>143.28</v>
       </c>
       <c r="F81">
-        <v>159.659</v>
+        <v>161.68</v>
       </c>
       <c r="G81">
         <v>40.8</v>
@@ -7929,37 +7929,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M81">
-        <v>32.0595272</v>
+        <v>32.465344</v>
       </c>
       <c r="N81">
-        <v>-14.53891495510204</v>
+        <v>-14.94473175510204</v>
       </c>
       <c r="O81">
-        <v>-3.053172140571427</v>
+        <v>-3.138393668571428</v>
       </c>
       <c r="P81">
-        <v>-11.48574281453061</v>
+        <v>-11.80633808653061</v>
       </c>
       <c r="Q81">
-        <v>-7.47574281453061</v>
+        <v>-7.796338086530612</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2978771929350285</v>
+        <v>0.3104810525817799</v>
       </c>
       <c r="T81">
-        <v>4.25038361242706</v>
+        <v>4.462902793048413</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1147655281525353</v>
+        <v>0.1133309590506286</v>
       </c>
       <c r="W81">
-        <v>0.1777550819469709</v>
+        <v>0.1780431434226338</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.546502515012073</v>
+        <v>0.539671233574422</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.204530725254463</v>
+        <v>0.206080725254463</v>
       </c>
       <c r="C82">
-        <v>-53.76920922159427</v>
+        <v>-56.38499376169457</v>
       </c>
       <c r="D82">
-        <v>67.11079077840574</v>
+        <v>66.51600623830542</v>
       </c>
       <c r="E82">
-        <v>143.28</v>
+        <v>145.301</v>
       </c>
       <c r="F82">
-        <v>161.68</v>
+        <v>163.701</v>
       </c>
       <c r="G82">
         <v>40.8</v>
@@ -8011,37 +8011,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M82">
-        <v>32.465344</v>
+        <v>32.8711608</v>
       </c>
       <c r="N82">
-        <v>-14.94473175510204</v>
+        <v>-15.35054855510204</v>
       </c>
       <c r="O82">
-        <v>-3.138393668571428</v>
+        <v>-3.223615196571428</v>
       </c>
       <c r="P82">
-        <v>-11.80633808653061</v>
+        <v>-12.12693335853061</v>
       </c>
       <c r="Q82">
-        <v>-7.796338086530612</v>
+        <v>-8.116933358530609</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3104810525817799</v>
+        <v>0.3244116342966105</v>
       </c>
       <c r="T82">
-        <v>4.462902793048413</v>
+        <v>4.697792413735171</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1133309590506286</v>
+        <v>0.1119318114080283</v>
       </c>
       <c r="W82">
-        <v>0.1780431434226338</v>
+        <v>0.1783240922692679</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.539671233574422</v>
+        <v>0.5330086257525156</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.206080725254463</v>
+        <v>0.207630725254463</v>
       </c>
       <c r="C83">
-        <v>-56.38499376169457</v>
+        <v>-58.99032809448249</v>
       </c>
       <c r="D83">
-        <v>66.51600623830542</v>
+        <v>65.93167190551752</v>
       </c>
       <c r="E83">
-        <v>145.301</v>
+        <v>147.322</v>
       </c>
       <c r="F83">
-        <v>163.701</v>
+        <v>165.722</v>
       </c>
       <c r="G83">
         <v>40.8</v>
@@ -8093,37 +8093,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M83">
-        <v>32.8711608</v>
+        <v>33.2769776</v>
       </c>
       <c r="N83">
-        <v>-15.35054855510204</v>
+        <v>-15.75636535510204</v>
       </c>
       <c r="O83">
-        <v>-3.223615196571428</v>
+        <v>-3.308836724571429</v>
       </c>
       <c r="P83">
-        <v>-12.12693335853061</v>
+        <v>-12.44752863053061</v>
       </c>
       <c r="Q83">
-        <v>-8.116933358530609</v>
+        <v>-8.437528630530613</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3244116342966105</v>
+        <v>0.3398900584241999</v>
       </c>
       <c r="T83">
-        <v>4.697792413735171</v>
+        <v>4.958780881164904</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1119318114080283</v>
+        <v>0.1105667893176865</v>
       </c>
       <c r="W83">
-        <v>0.1783240922692679</v>
+        <v>0.1785981887050086</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5330086257525156</v>
+        <v>0.5265085205604116</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.207630725254463</v>
+        <v>0.209180725254463</v>
       </c>
       <c r="C84">
-        <v>-58.99032809448249</v>
+        <v>-61.58548523265208</v>
       </c>
       <c r="D84">
-        <v>65.93167190551752</v>
+        <v>65.35751476734795</v>
       </c>
       <c r="E84">
-        <v>147.322</v>
+        <v>149.343</v>
       </c>
       <c r="F84">
-        <v>165.722</v>
+        <v>167.743</v>
       </c>
       <c r="G84">
         <v>40.8</v>
@@ -8175,37 +8175,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M84">
-        <v>33.2769776</v>
+        <v>33.68279440000001</v>
       </c>
       <c r="N84">
-        <v>-15.75636535510204</v>
+        <v>-16.16218215510204</v>
       </c>
       <c r="O84">
-        <v>-3.308836724571429</v>
+        <v>-3.394058252571429</v>
       </c>
       <c r="P84">
-        <v>-12.44752863053061</v>
+        <v>-12.76812390253061</v>
       </c>
       <c r="Q84">
-        <v>-8.437528630530613</v>
+        <v>-8.758123902530615</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3398900584241999</v>
+        <v>0.3571894736256235</v>
       </c>
       <c r="T84">
-        <v>4.958780881164904</v>
+        <v>5.250473874174605</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1105667893176865</v>
+        <v>0.1092346593259071</v>
       </c>
       <c r="W84">
-        <v>0.1785981887050086</v>
+        <v>0.1788656804073579</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5265085205604116</v>
+        <v>0.5201650444090814</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.209180725254463</v>
+        <v>0.210730725254463</v>
       </c>
       <c r="C85">
-        <v>-61.58548523265208</v>
+        <v>-64.17072876102077</v>
       </c>
       <c r="D85">
-        <v>65.35751476734795</v>
+        <v>64.79327123897924</v>
       </c>
       <c r="E85">
-        <v>149.343</v>
+        <v>151.364</v>
       </c>
       <c r="F85">
-        <v>167.743</v>
+        <v>169.764</v>
       </c>
       <c r="G85">
         <v>40.8</v>
@@ -8257,37 +8257,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M85">
-        <v>33.68279440000001</v>
+        <v>34.0886112</v>
       </c>
       <c r="N85">
-        <v>-16.16218215510204</v>
+        <v>-16.56799895510204</v>
       </c>
       <c r="O85">
-        <v>-3.394058252571429</v>
+        <v>-3.479279780571428</v>
       </c>
       <c r="P85">
-        <v>-12.76812390253061</v>
+        <v>-13.08871917453061</v>
       </c>
       <c r="Q85">
-        <v>-8.758123902530615</v>
+        <v>-9.078719174530614</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3571894736256235</v>
+        <v>0.376651315727225</v>
       </c>
       <c r="T85">
-        <v>5.250473874174605</v>
+        <v>5.578628491310519</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1092346593259071</v>
+        <v>0.1079342467148844</v>
       </c>
       <c r="W85">
-        <v>0.1788656804073579</v>
+        <v>0.1791268032596512</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5201650444090814</v>
+        <v>0.5139726034042114</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.210730725254463</v>
+        <v>0.212280725254463</v>
       </c>
       <c r="C86">
-        <v>-64.17072876102074</v>
+        <v>-66.7463132400092</v>
       </c>
       <c r="D86">
-        <v>64.79327123897924</v>
+        <v>64.2386867599908</v>
       </c>
       <c r="E86">
-        <v>151.364</v>
+        <v>153.385</v>
       </c>
       <c r="F86">
-        <v>169.764</v>
+        <v>171.785</v>
       </c>
       <c r="G86">
         <v>40.8</v>
@@ -8339,37 +8339,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M86">
-        <v>34.0886112</v>
+        <v>34.494428</v>
       </c>
       <c r="N86">
-        <v>-16.56799895510203</v>
+        <v>-16.97381575510204</v>
       </c>
       <c r="O86">
-        <v>-3.479279780571427</v>
+        <v>-3.564501308571428</v>
       </c>
       <c r="P86">
-        <v>-13.08871917453061</v>
+        <v>-13.40931444653061</v>
       </c>
       <c r="Q86">
-        <v>-9.078719174530606</v>
+        <v>-9.39931444653061</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3766513157272248</v>
+        <v>0.3987080701090399</v>
       </c>
       <c r="T86">
-        <v>5.578628491310514</v>
+        <v>5.950537057397883</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1079342467148844</v>
+        <v>0.1066644320476505</v>
       </c>
       <c r="W86">
-        <v>0.1791268032596512</v>
+        <v>0.1793817820448318</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5139726034042116</v>
+        <v>0.5079258668935738</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.212280725254463</v>
+        <v>0.213830725254463</v>
       </c>
       <c r="C87">
-        <v>-66.7463132400092</v>
+        <v>-69.31248458857567</v>
       </c>
       <c r="D87">
-        <v>64.2386867599908</v>
+        <v>63.69351541142432</v>
       </c>
       <c r="E87">
-        <v>153.385</v>
+        <v>155.406</v>
       </c>
       <c r="F87">
-        <v>171.785</v>
+        <v>173.806</v>
       </c>
       <c r="G87">
         <v>40.8</v>
@@ -8421,37 +8421,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M87">
-        <v>34.494428</v>
+        <v>34.9002448</v>
       </c>
       <c r="N87">
-        <v>-16.97381575510204</v>
+        <v>-17.37963255510203</v>
       </c>
       <c r="O87">
-        <v>-3.564501308571428</v>
+        <v>-3.649722836571427</v>
       </c>
       <c r="P87">
-        <v>-13.40931444653061</v>
+        <v>-13.72990971853061</v>
       </c>
       <c r="Q87">
-        <v>-9.39931444653061</v>
+        <v>-9.719909718530607</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3987080701090399</v>
+        <v>0.4239157894025427</v>
       </c>
       <c r="T87">
-        <v>5.950537057397883</v>
+        <v>6.375575418640588</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1066644320476505</v>
+        <v>0.1054241479540731</v>
       </c>
       <c r="W87">
-        <v>0.1793817820448318</v>
+        <v>0.1796308310908221</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5079258668935738</v>
+        <v>0.5020197521622531</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.213830725254463</v>
+        <v>0.2466141397893296</v>
       </c>
       <c r="C88">
-        <v>-69.31248458857567</v>
+        <v>-81.02645712770575</v>
       </c>
       <c r="D88">
-        <v>63.69351541142432</v>
+        <v>54.00054287229425</v>
       </c>
       <c r="E88">
-        <v>155.406</v>
+        <v>157.427</v>
       </c>
       <c r="F88">
-        <v>173.806</v>
+        <v>175.827</v>
       </c>
       <c r="G88">
         <v>40.8</v>
@@ -8503,45 +8503,45 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M88">
-        <v>34.9002448</v>
+        <v>41.4600066</v>
       </c>
       <c r="N88">
-        <v>-17.37963255510203</v>
+        <v>-23.93939435510204</v>
       </c>
       <c r="O88">
-        <v>-3.649722836571427</v>
+        <v>-5.027272814571428</v>
       </c>
       <c r="P88">
-        <v>-13.72990971853061</v>
+        <v>-18.91212154053061</v>
       </c>
       <c r="Q88">
-        <v>-9.719909718530607</v>
+        <v>-14.90212154053061</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4239157894025427</v>
+        <v>0.4590278850094041</v>
       </c>
       <c r="T88">
-        <v>6.375575418640588</v>
+        <v>6.967615793367553</v>
       </c>
       <c r="U88">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1054241479540731</v>
+        <v>0.08874404210607559</v>
       </c>
       <c r="W88">
-        <v>0.1796308310908221</v>
+        <v>0.2148741548713874</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.5020197521622531</v>
+        <v>0.422590676695598</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2466141397893296</v>
+        <v>0.2485141397893295</v>
       </c>
       <c r="C89">
-        <v>-81.02645712770575</v>
+        <v>-83.51956983031599</v>
       </c>
       <c r="D89">
-        <v>54.00054287229425</v>
+        <v>53.52843016968399</v>
       </c>
       <c r="E89">
-        <v>157.427</v>
+        <v>159.448</v>
       </c>
       <c r="F89">
-        <v>175.827</v>
+        <v>177.848</v>
       </c>
       <c r="G89">
         <v>40.8</v>
@@ -8585,37 +8585,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M89">
-        <v>41.4600066</v>
+        <v>41.9365584</v>
       </c>
       <c r="N89">
-        <v>-23.93939435510204</v>
+        <v>-24.41594615510203</v>
       </c>
       <c r="O89">
-        <v>-5.027272814571428</v>
+        <v>-5.127348692571427</v>
       </c>
       <c r="P89">
-        <v>-18.91212154053061</v>
+        <v>-19.28859746253061</v>
       </c>
       <c r="Q89">
-        <v>-14.90212154053061</v>
+        <v>-15.27859746253061</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4590278850094041</v>
+        <v>0.4934635420935211</v>
       </c>
       <c r="T89">
-        <v>6.967615793367553</v>
+        <v>7.54825044281485</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08874404210607559</v>
+        <v>0.08773558708214292</v>
       </c>
       <c r="W89">
-        <v>0.2148741548713874</v>
+        <v>0.2151119485660307</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.422590676695598</v>
+        <v>0.4177885099149663</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2485141397893295</v>
+        <v>0.2504141397893295</v>
       </c>
       <c r="C90">
-        <v>-83.51956983031599</v>
+        <v>-86.00449896259678</v>
       </c>
       <c r="D90">
-        <v>53.52843016968399</v>
+        <v>53.06450103740321</v>
       </c>
       <c r="E90">
-        <v>159.448</v>
+        <v>161.469</v>
       </c>
       <c r="F90">
-        <v>177.848</v>
+        <v>179.869</v>
       </c>
       <c r="G90">
         <v>40.8</v>
@@ -8667,37 +8667,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M90">
-        <v>41.9365584</v>
+        <v>42.4131102</v>
       </c>
       <c r="N90">
-        <v>-24.41594615510203</v>
+        <v>-24.89249795510204</v>
       </c>
       <c r="O90">
-        <v>-5.127348692571427</v>
+        <v>-5.227424570571428</v>
       </c>
       <c r="P90">
-        <v>-19.28859746253061</v>
+        <v>-19.66507338453061</v>
       </c>
       <c r="Q90">
-        <v>-15.27859746253061</v>
+        <v>-15.65507338453061</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4934635420935211</v>
+        <v>0.5341602277383866</v>
       </c>
       <c r="T90">
-        <v>7.54825044281485</v>
+        <v>8.234455028525291</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08773558708214292</v>
+        <v>0.08674979396886041</v>
       </c>
       <c r="W90">
-        <v>0.2151119485660307</v>
+        <v>0.2153443985821427</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4177885099149663</v>
+        <v>0.4130942569945734</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2504141397893295</v>
+        <v>0.2523141397893295</v>
       </c>
       <c r="C91">
-        <v>-86.00449896259678</v>
+        <v>-88.48145547643446</v>
       </c>
       <c r="D91">
-        <v>53.06450103740321</v>
+        <v>52.60854452356553</v>
       </c>
       <c r="E91">
-        <v>161.469</v>
+        <v>163.49</v>
       </c>
       <c r="F91">
-        <v>179.869</v>
+        <v>181.89</v>
       </c>
       <c r="G91">
         <v>40.8</v>
@@ -8749,37 +8749,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M91">
-        <v>42.4131102</v>
+        <v>42.889662</v>
       </c>
       <c r="N91">
-        <v>-24.89249795510204</v>
+        <v>-25.36904975510204</v>
       </c>
       <c r="O91">
-        <v>-5.227424570571428</v>
+        <v>-5.327500448571429</v>
       </c>
       <c r="P91">
-        <v>-19.66507338453061</v>
+        <v>-20.04154930653061</v>
       </c>
       <c r="Q91">
-        <v>-15.65507338453061</v>
+        <v>-16.03154930653061</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5341602277383866</v>
+        <v>0.5829962505122253</v>
       </c>
       <c r="T91">
-        <v>8.234455028525291</v>
+        <v>9.05790053137782</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08674979396886041</v>
+        <v>0.0857859073692064</v>
       </c>
       <c r="W91">
-        <v>0.2153443985821427</v>
+        <v>0.2155716830423411</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4130942569945734</v>
+        <v>0.4085043208057447</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2523141397893295</v>
+        <v>0.2542141397893296</v>
       </c>
       <c r="C92">
-        <v>-88.48145547643446</v>
+        <v>-90.95064313507085</v>
       </c>
       <c r="D92">
-        <v>52.60854452356553</v>
+        <v>52.16035686492916</v>
       </c>
       <c r="E92">
-        <v>163.49</v>
+        <v>165.511</v>
       </c>
       <c r="F92">
-        <v>181.89</v>
+        <v>183.911</v>
       </c>
       <c r="G92">
         <v>40.8</v>
@@ -8831,37 +8831,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M92">
-        <v>42.889662</v>
+        <v>43.3662138</v>
       </c>
       <c r="N92">
-        <v>-25.36904975510204</v>
+        <v>-25.84560155510204</v>
       </c>
       <c r="O92">
-        <v>-5.327500448571429</v>
+        <v>-5.427576326571429</v>
       </c>
       <c r="P92">
-        <v>-20.04154930653061</v>
+        <v>-20.41802522853061</v>
       </c>
       <c r="Q92">
-        <v>-16.03154930653061</v>
+        <v>-16.40802522853061</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5829962505122253</v>
+        <v>0.6426847227913616</v>
       </c>
       <c r="T92">
-        <v>9.05790053137782</v>
+        <v>10.06433392375314</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0857859073692064</v>
+        <v>0.08484320509042391</v>
       </c>
       <c r="W92">
-        <v>0.2155716830423411</v>
+        <v>0.2157939722396781</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4085043208057447</v>
+        <v>0.4040152623353519</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2542141397893296</v>
+        <v>0.2561141397893296</v>
       </c>
       <c r="C93">
-        <v>-90.95064313507085</v>
+        <v>-93.41225881672744</v>
       </c>
       <c r="D93">
-        <v>52.16035686492916</v>
+        <v>51.71974118327257</v>
       </c>
       <c r="E93">
-        <v>165.511</v>
+        <v>167.532</v>
       </c>
       <c r="F93">
-        <v>183.911</v>
+        <v>185.932</v>
       </c>
       <c r="G93">
         <v>40.8</v>
@@ -8913,37 +8913,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M93">
-        <v>43.3662138</v>
+        <v>43.84276560000001</v>
       </c>
       <c r="N93">
-        <v>-25.84560155510204</v>
+        <v>-26.32215335510205</v>
       </c>
       <c r="O93">
-        <v>-5.427576326571429</v>
+        <v>-5.52765220457143</v>
       </c>
       <c r="P93">
-        <v>-20.41802522853061</v>
+        <v>-20.79450115053061</v>
       </c>
       <c r="Q93">
-        <v>-16.40802522853061</v>
+        <v>-16.78450115053062</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6426847227913616</v>
+        <v>0.7172953131402819</v>
       </c>
       <c r="T93">
-        <v>10.06433392375314</v>
+        <v>11.32237566422228</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08484320509042391</v>
+        <v>0.08392099633944103</v>
       </c>
       <c r="W93">
-        <v>0.2157939722396781</v>
+        <v>0.2160114290631598</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4040152623353519</v>
+        <v>0.3996237920925764</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2561141397893296</v>
+        <v>0.2580141397893296</v>
       </c>
       <c r="C94">
-        <v>-93.41225881672744</v>
+        <v>-95.86649280296953</v>
       </c>
       <c r="D94">
-        <v>51.71974118327257</v>
+        <v>51.28650719703048</v>
       </c>
       <c r="E94">
-        <v>167.532</v>
+        <v>169.553</v>
       </c>
       <c r="F94">
-        <v>185.932</v>
+        <v>187.953</v>
       </c>
       <c r="G94">
         <v>40.8</v>
@@ -8995,37 +8995,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M94">
-        <v>43.84276560000001</v>
+        <v>44.3193174</v>
       </c>
       <c r="N94">
-        <v>-26.32215335510205</v>
+        <v>-26.79870515510204</v>
       </c>
       <c r="O94">
-        <v>-5.52765220457143</v>
+        <v>-5.627728082571428</v>
       </c>
       <c r="P94">
-        <v>-20.79450115053061</v>
+        <v>-21.17097707253061</v>
       </c>
       <c r="Q94">
-        <v>-16.78450115053062</v>
+        <v>-17.16097707253061</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7172953131402819</v>
+        <v>0.8132232150174651</v>
       </c>
       <c r="T94">
-        <v>11.32237566422228</v>
+        <v>12.93985790196832</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08392099633944103</v>
+        <v>0.08301862003471586</v>
       </c>
       <c r="W94">
-        <v>0.2160114290631598</v>
+        <v>0.216224209395814</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3996237920925764</v>
+        <v>0.3953267620700756</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2580141397893296</v>
+        <v>0.2599141397893295</v>
       </c>
       <c r="C95">
-        <v>-95.86649280296953</v>
+        <v>-98.31352905269804</v>
       </c>
       <c r="D95">
-        <v>51.28650719703048</v>
+        <v>50.86047094730198</v>
       </c>
       <c r="E95">
-        <v>169.553</v>
+        <v>171.574</v>
       </c>
       <c r="F95">
-        <v>187.953</v>
+        <v>189.974</v>
       </c>
       <c r="G95">
         <v>40.8</v>
@@ -9077,37 +9077,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M95">
-        <v>44.3193174</v>
+        <v>44.79586920000001</v>
       </c>
       <c r="N95">
-        <v>-26.79870515510204</v>
+        <v>-27.27525695510204</v>
       </c>
       <c r="O95">
-        <v>-5.627728082571428</v>
+        <v>-5.727803960571429</v>
       </c>
       <c r="P95">
-        <v>-21.17097707253061</v>
+        <v>-21.54745299453062</v>
       </c>
       <c r="Q95">
-        <v>-17.16097707253061</v>
+        <v>-17.53745299453062</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8132232150174651</v>
+        <v>0.9411270841870429</v>
       </c>
       <c r="T95">
-        <v>12.93985790196832</v>
+        <v>15.09650088562971</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.08301862003471586</v>
+        <v>0.08213544322583589</v>
       </c>
       <c r="W95">
-        <v>0.216224209395814</v>
+        <v>0.2164324624873479</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3953267620700756</v>
+        <v>0.3911211582182662</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2599141397893295</v>
+        <v>0.2618141397893295</v>
       </c>
       <c r="C96">
-        <v>-98.31352905269804</v>
+        <v>-100.7535454625972</v>
       </c>
       <c r="D96">
-        <v>50.86047094730198</v>
+        <v>50.44145453740283</v>
       </c>
       <c r="E96">
-        <v>171.574</v>
+        <v>173.595</v>
       </c>
       <c r="F96">
-        <v>189.974</v>
+        <v>191.995</v>
       </c>
       <c r="G96">
         <v>40.8</v>
@@ -9159,37 +9159,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M96">
-        <v>44.79586920000001</v>
+        <v>45.272421</v>
       </c>
       <c r="N96">
-        <v>-27.27525695510204</v>
+        <v>-27.75180875510204</v>
       </c>
       <c r="O96">
-        <v>-5.727803960571429</v>
+        <v>-5.827879838571429</v>
       </c>
       <c r="P96">
-        <v>-21.54745299453062</v>
+        <v>-21.92392891653061</v>
       </c>
       <c r="Q96">
-        <v>-17.53745299453062</v>
+        <v>-17.91392891653062</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9411270841870429</v>
+        <v>1.120192501024452</v>
       </c>
       <c r="T96">
-        <v>15.09650088562971</v>
+        <v>18.11580106275566</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08213544322583589</v>
+        <v>0.08127085961293237</v>
       </c>
       <c r="W96">
-        <v>0.2164324624873479</v>
+        <v>0.2166363313032706</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3911211582182662</v>
+        <v>0.3870040933949161</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2618141397893295</v>
+        <v>0.2637141397893296</v>
       </c>
       <c r="C97">
-        <v>-100.7535454625972</v>
+        <v>-103.1867141148133</v>
       </c>
       <c r="D97">
-        <v>50.44145453740283</v>
+        <v>50.02928588518668</v>
       </c>
       <c r="E97">
-        <v>173.595</v>
+        <v>175.616</v>
       </c>
       <c r="F97">
-        <v>191.995</v>
+        <v>194.016</v>
       </c>
       <c r="G97">
         <v>40.8</v>
@@ -9241,37 +9241,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M97">
-        <v>45.272421</v>
+        <v>45.7489728</v>
       </c>
       <c r="N97">
-        <v>-27.75180875510204</v>
+        <v>-28.22836055510204</v>
       </c>
       <c r="O97">
-        <v>-5.827879838571429</v>
+        <v>-5.927955716571429</v>
       </c>
       <c r="P97">
-        <v>-21.92392891653061</v>
+        <v>-22.30040483853061</v>
       </c>
       <c r="Q97">
-        <v>-17.91392891653062</v>
+        <v>-18.29040483853061</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.120192501024452</v>
+        <v>1.388790626280566</v>
       </c>
       <c r="T97">
-        <v>18.11580106275566</v>
+        <v>22.64475132844459</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.08127085961293237</v>
+        <v>0.08042428815863099</v>
       </c>
       <c r="W97">
-        <v>0.2166363313032706</v>
+        <v>0.2168359528521948</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3870040933949161</v>
+        <v>0.3829728007553856</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2637141397893296</v>
+        <v>0.2656141397893296</v>
       </c>
       <c r="C98">
-        <v>-103.1867141148133</v>
+        <v>-105.6132015125892</v>
       </c>
       <c r="D98">
-        <v>50.02928588518668</v>
+        <v>49.62379848741079</v>
       </c>
       <c r="E98">
-        <v>175.616</v>
+        <v>177.637</v>
       </c>
       <c r="F98">
-        <v>194.016</v>
+        <v>196.037</v>
       </c>
       <c r="G98">
         <v>40.8</v>
@@ -9323,37 +9323,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M98">
-        <v>45.7489728</v>
+        <v>46.2255246</v>
       </c>
       <c r="N98">
-        <v>-28.22836055510204</v>
+        <v>-28.70491235510204</v>
       </c>
       <c r="O98">
-        <v>-5.927955716571427</v>
+        <v>-6.028031594571428</v>
       </c>
       <c r="P98">
-        <v>-22.30040483853061</v>
+        <v>-22.67688076053061</v>
       </c>
       <c r="Q98">
-        <v>-18.29040483853061</v>
+        <v>-18.66688076053061</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.388790626280562</v>
+        <v>1.836454168374083</v>
       </c>
       <c r="T98">
-        <v>22.64475132844453</v>
+        <v>30.19300177125938</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08042428815863101</v>
+        <v>0.0795951717858616</v>
       </c>
       <c r="W98">
-        <v>0.2168359528521948</v>
+        <v>0.2170314584928938</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3829728007553858</v>
+        <v>0.3790246275517219</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2656141397893296</v>
+        <v>0.2675141397893295</v>
       </c>
       <c r="C99">
-        <v>-105.6132015125892</v>
+        <v>-108.0331688045313</v>
       </c>
       <c r="D99">
-        <v>49.62379848741079</v>
+        <v>49.22483119546874</v>
       </c>
       <c r="E99">
-        <v>177.637</v>
+        <v>179.658</v>
       </c>
       <c r="F99">
-        <v>196.037</v>
+        <v>198.058</v>
       </c>
       <c r="G99">
         <v>40.8</v>
@@ -9405,37 +9405,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M99">
-        <v>46.2255246</v>
+        <v>46.7020764</v>
       </c>
       <c r="N99">
-        <v>-28.70491235510204</v>
+        <v>-29.18146415510204</v>
       </c>
       <c r="O99">
-        <v>-6.028031594571428</v>
+        <v>-6.128107472571428</v>
       </c>
       <c r="P99">
-        <v>-22.67688076053061</v>
+        <v>-23.05335668253061</v>
       </c>
       <c r="Q99">
-        <v>-18.66688076053061</v>
+        <v>-19.04335668253061</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.836454168374083</v>
+        <v>2.731781252561124</v>
       </c>
       <c r="T99">
-        <v>30.19300177125938</v>
+        <v>45.28950265688906</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0795951717858616</v>
+        <v>0.07878297615539363</v>
       </c>
       <c r="W99">
-        <v>0.2170314584928938</v>
+        <v>0.2172229742225582</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3790246275517219</v>
+        <v>0.3751570293113983</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2675141397893295</v>
+        <v>0.2694141397893296</v>
       </c>
       <c r="C100">
-        <v>-108.0331688045313</v>
+        <v>-110.4467719981449</v>
       </c>
       <c r="D100">
-        <v>49.22483119546874</v>
+        <v>48.83222800185509</v>
       </c>
       <c r="E100">
-        <v>179.658</v>
+        <v>181.679</v>
       </c>
       <c r="F100">
-        <v>198.058</v>
+        <v>200.079</v>
       </c>
       <c r="G100">
         <v>40.8</v>
@@ -9487,37 +9487,37 @@
         <v>17.52061224489796</v>
       </c>
       <c r="M100">
-        <v>46.7020764</v>
+        <v>47.1786282</v>
       </c>
       <c r="N100">
-        <v>-29.18146415510204</v>
+        <v>-29.65801595510204</v>
       </c>
       <c r="O100">
-        <v>-6.128107472571428</v>
+        <v>-6.228183350571427</v>
       </c>
       <c r="P100">
-        <v>-23.05335668253061</v>
+        <v>-23.42983260453061</v>
       </c>
       <c r="Q100">
-        <v>-19.04335668253061</v>
+        <v>-19.41983260453061</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.731781252561124</v>
+        <v>5.417762505122249</v>
       </c>
       <c r="T100">
-        <v>45.28950265688906</v>
+        <v>90.57900531377813</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07878297615539363</v>
+        <v>0.07798718851746037</v>
       </c>
       <c r="W100">
-        <v>0.2172229742225582</v>
+        <v>0.2174106209475829</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3751570293113983</v>
+        <v>0.3713675643688589</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2694141397893296</v>
-      </c>
-      <c r="C101">
-        <v>-110.4467719981449</v>
-      </c>
-      <c r="D101">
-        <v>48.83222800185509</v>
-      </c>
-      <c r="E101">
-        <v>181.679</v>
-      </c>
-      <c r="F101">
-        <v>200.079</v>
-      </c>
-      <c r="G101">
-        <v>40.8</v>
-      </c>
-      <c r="H101">
-        <v>183.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>21.53061224489796</v>
-      </c>
-      <c r="K101">
-        <v>4.01</v>
-      </c>
-      <c r="L101">
-        <v>17.52061224489796</v>
-      </c>
-      <c r="M101">
-        <v>47.1786282</v>
-      </c>
-      <c r="N101">
-        <v>-29.65801595510204</v>
-      </c>
-      <c r="O101">
-        <v>-6.228183350571427</v>
-      </c>
-      <c r="P101">
-        <v>-23.42983260453061</v>
-      </c>
-      <c r="Q101">
-        <v>-19.41983260453061</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.417762505122249</v>
-      </c>
-      <c r="T101">
-        <v>90.57900531377813</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07798718851746037</v>
-      </c>
-      <c r="W101">
-        <v>0.2174106209475829</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3713675643688589</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
